--- a/wbs-assessment/WBS_Assessment_GTM.xlsx
+++ b/wbs-assessment/WBS_Assessment_GTM.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="WBS" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Timeline" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Riepilogo" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sheet" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Parametri" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Ruoli" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Riepilogo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parametri" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ruoli" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$5:$Z$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$5:$AA$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'WBS'!$5:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,14 +24,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0;-#,##0;&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;€&quot;;-#,##0.00\ &quot;€&quot;;&quot;-&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;-#,##0.0;&quot;-&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00;-#,##0.00;&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="&quot;S&quot;0"/>
     <numFmt numFmtId="168" formatCode=";;;"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +65,12 @@
     </font>
     <font>
       <name val="Manrope"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Manrope"/>
       <color rgb="00000000"/>
       <sz val="9"/>
     </font>
@@ -75,27 +82,8 @@
     <font>
       <name val="Manrope"/>
       <b val="1"/>
-      <i val="1"/>
       <color rgb="003A3A3A"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Manrope"/>
-      <i val="1"/>
-      <color rgb="006E6E6E"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Manrope"/>
-      <b val="1"/>
-      <color rgb="003A3A3A"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Manrope"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -185,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -207,25 +195,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -240,18 +228,48 @@
     <xf numFmtId="165" fontId="3" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="8" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -259,73 +277,28 @@
     <xf numFmtId="165" fontId="8" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="7" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,9 +445,30 @@
     <author>WBS</author>
   </authors>
   <commentList>
-    <comment ref="C6" authorId="0" shapeId="0">
+    <comment ref="T5" authorId="0" shapeId="0">
       <text>
-        <t>Tariffa non ancora fornita. Finché la cella resta vuota, la colonna «Costo totale» della WBS vale 0.</t>
+        <t>Calcolata: N. incontri × Durata incontro (h) × N. persone ÷ Ore per giornata.
+Per cambiare l'impegno, agire su quelle tre colonne.</t>
+      </text>
+    </comment>
+    <comment ref="U5" authorId="0" shapeId="0">
+      <text>
+        <t>Stime Impresoft. L'Offerta quantifica solo le ore erogate al cliente e il numero di trasferte: sul back office non dice nulla.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>WBS</author>
+  </authors>
+  <commentList>
+    <comment ref="C7" authorId="0" shapeId="0">
+      <text>
+        <t>Le tre tariffe orarie non sono state fornite. Finché restano vuote, tutte le colonne di costo valgono 0.</t>
       </text>
     </comment>
   </commentList>
@@ -770,41 +764,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:AA17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="68" customWidth="1" min="10" max="10"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
     <col width="40" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="13"/>
     <col width="44" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="9" customWidth="1" min="21" max="21"/>
-    <col width="38" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="40" customWidth="1" min="23" max="23"/>
     <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="15" customWidth="1" min="25" max="25"/>
-    <col width="46" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="52" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>›  WORK BREAKDOWN STRUCTURE — PROGETTO DI ASSESSMENT GO-TO-MARKET</t>
+          <t>›  WORK BREAKDOWN STRUCTURE — REVOPS ASSESSMENT B2B E B2C · LAICA S.P.A.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -832,18 +827,19 @@
       <c r="X1" s="2" t="n"/>
       <c r="Y1" s="2" t="n"/>
       <c r="Z1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="24" customHeight="1">
+      <c r="AA1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>LEGENDA — Le colonne con intestazione GIALLA sono da compilare a mano: le loro celle portano un riquadro nero. Le celle su fondo GRIGIO sono calcolate da formula e non vanno modificate. Tariffe e ore per giornata si impostano nel foglio «Parametri», i nomi del team nel foglio «Ruoli».</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="26" customHeight="1">
+          <t>Allineata all'Offerta CX260803_Off_Laica_RevOps assessment B2B e B2C v1.1 del 28 ago 2026.  ·  LEGENDA — Colonne con intestazione GIALLA: da compilare a mano, celle con riquadro nero. Celle su fondo GRIGIO: calcolate da formula. Tariffe, ore per giornata e costi di trasferta si impostano nel foglio «Parametri»; i nomi del team nel foglio «Ruoli».</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Le colonne «gg Front office / Back office / Viaggio» esprimono GIORNATE-UOMO aggregate, non giorni di calendario: 2 consulenti per mezza giornata dal cliente = 1 giornata front. La composizione della squadra si descrive nella colonna «Delivery». Le ore di viaggio sono incluse nel monte ore.</t>
+          <t>gg Front office e gg Viaggio sono CALCOLATE: front = n. incontri × durata × n. persone ÷ ore per giornata; viaggio = n. incontri × n. persone × ore di viaggio ÷ ore per giornata, solo sulle fasi in presenza. L'unico input di effort è gg Back office — e il contratto non lo quantifica in nessun punto: quei valori sono STIME Impresoft.</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -871,6 +867,7 @@
       <c r="X3" s="5" t="n"/>
       <c r="Y3" s="5" t="n"/>
       <c r="Z3" s="5" t="n"/>
+      <c r="AA3" s="5" t="n"/>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
@@ -880,7 +877,8 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Cod. WBS</t>
+          <t>Cod.
+WBS</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -970,51 +968,57 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
+          <t>N.
+persone</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr">
+        <is>
           <t>gg Front
 office</t>
         </is>
       </c>
-      <c r="T5" s="7" t="inlineStr">
+      <c r="U5" s="7" t="inlineStr">
         <is>
           <t>gg Back
 office</t>
         </is>
       </c>
-      <c r="U5" s="7" t="inlineStr">
+      <c r="V5" s="6" t="inlineStr">
         <is>
           <t>gg
 Viaggio</t>
         </is>
       </c>
-      <c r="V5" s="6" t="inlineStr">
+      <c r="W5" s="6" t="inlineStr">
         <is>
           <t>Delivery (composizione team)</t>
         </is>
       </c>
-      <c r="W5" s="6" t="inlineStr">
+      <c r="X5" s="6" t="inlineStr">
         <is>
           <t>Tot.
 giornate</t>
         </is>
       </c>
-      <c r="X5" s="6" t="inlineStr">
+      <c r="Y5" s="6" t="inlineStr">
         <is>
           <t>Ore
 totali</t>
         </is>
       </c>
-      <c r="Y5" s="6" t="inlineStr">
+      <c r="Z5" s="6" t="inlineStr">
         <is>
           <t>Costo totale</t>
         </is>
       </c>
-      <c r="Z5" s="6" t="inlineStr">
+      <c r="AA5" s="6" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="78" customHeight="1">
+    <row r="6" ht="96" customHeight="1">
       <c r="A6" s="8" t="n">
         <v>1</v>
       </c>
@@ -1025,7 +1029,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Kick off e raccolta dati</t>
+          <t>Kick-off e analisi preliminare dei dati</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -1047,7 +1051,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="12">
         <f>IF(AND(G6&lt;&gt;"",H6&lt;&gt;""),G6+H6-1,"")</f>
@@ -1055,66 +1059,83 @@
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>Incontro di avvio in remoto con i team di progetto di entrambe le parti. Si condividono obiettivi e perimetro dell'assessment, si presenta il team e si calendarizzano gli incontri successivi. Nella seconda parte si illustra la struttura dei dati richiesta al cliente, si chiariscono dubbi e domande e si concorda la data di consegna degli export, fissata entro una settimana dal kick off. Il lead time della fase coincide con il tempo necessario al cliente per predisporre e trasmettere gli export.</t>
+          <t>Incontro di avvio in remoto che sancisce l'apertura ufficiale del progetto: allineamento sulla governance, presentazione dei team e delle regole d'ingaggio tra tutti gli attori operativi e decisionali, condivisione della roadmap progettuale e del piano temporale di dettaglio con le date delle sessioni. Nella stessa sede si concordano le estrazioni da CRM ed ERP necessarie a comprendere la struttura dei dati di clienti e ordini, i punti di accesso all'informazione e la gestione dati attuale. L'analisi della base dati è condotta in modalità asincrona dai consulenti.</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>Invio dell'invito e fissaggio dell'incontro a cura del Commerciale.</t>
+          <t>Convocazione dell'incontro a cura del Commerciale; predisposizione delle slide di kick-off e della proposta di piano temporale (Gantt).</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>Invio, a cura del Project Manager, del documento presentato e del tracciato dei dati richiesti.</t>
+          <t>E-mail di debrief con slide di kick-off e piano di lavoro definitivo allegati in PDF; analisi asincrona delle estrazioni ricevute.</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
-          <t>Export dei dati trasmessi via email entro 5 giorni lavorativi dal kick off.</t>
+          <t>Estrazioni da CRM ed ERP su clienti e ordini; contatti dei referenti di progetto con adeguata autorità decisionale.</t>
         </is>
       </c>
       <c r="N6" s="9" t="inlineStr">
         <is>
-          <t>Obiettivi e perimetro condivisi · calendario degli incontri · tracciato dati concordato.</t>
+          <t>Governance di progetto condivisa · piano temporale definitivo · e-mail di debrief con slide e piano in PDF · analisi preliminare della base dati.</t>
         </is>
       </c>
       <c r="O6" s="9" t="inlineStr">
         <is>
-          <t>Commerciale (convocazione) → Project Manager (follow-up)</t>
+          <t>Commerciale (convocazione) → Project Manager (presidio)</t>
         </is>
       </c>
       <c r="P6" s="9" t="inlineStr">
         <is>
-          <t>Team di progetto completo, entrambe le parti</t>
+          <t>Impresoft: 3 persone. Laica: Managing Director, CMO, CFO, CSO, referenti gestione dati / IT.</t>
         </is>
       </c>
       <c r="Q6" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="R6" s="13" t="n"/>
-      <c r="S6" s="13" t="n"/>
-      <c r="T6" s="13" t="n"/>
-      <c r="U6" s="13" t="n"/>
-      <c r="V6" s="9" t="n"/>
-      <c r="W6" s="14">
-        <f>IF(COUNT(S6:U6)=0,"",SUM(S6:U6))</f>
-        <v/>
+      <c r="R6" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S6" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" s="14">
+        <f>IF(OR(Q6="",R6="",S6=""),0,Q6*R6*S6/Parametri!$C$6)</f>
+        <v/>
+      </c>
+      <c r="U6" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" s="14">
+        <f>IF(AND(E6="In presenza",Q6&lt;&gt;"",S6&lt;&gt;""),Q6*S6*Parametri!$C$10/Parametri!$C$6,0)</f>
+        <v/>
+      </c>
+      <c r="W6" s="9" t="inlineStr">
+        <is>
+          <t>3 persone in remoto (1 facilitatore senior + 2 RevOps Consultant junior)</t>
+        </is>
       </c>
       <c r="X6" s="14">
-        <f>IF(W6="","",W6*Parametri!$C$5)</f>
-        <v/>
-      </c>
-      <c r="Y6" s="15">
-        <f>IF(COUNT(S6:U6)=0,"",S6*Parametri!$C$5*Parametri!$C$6+T6*Parametri!$C$5*Parametri!$C$7+U6*Parametri!$C$5*Parametri!$C$8)</f>
-        <v/>
-      </c>
-      <c r="Z6" s="9" t="inlineStr">
-        <is>
-          <t>Vincolo: la consegna degli export non può superare 1 settimana dal kick off.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="78" customHeight="1">
+        <f>T6+U6+V6</f>
+        <v/>
+      </c>
+      <c r="Y6" s="14">
+        <f>X6*Parametri!$C$6</f>
+        <v/>
+      </c>
+      <c r="Z6" s="15">
+        <f>T6*Parametri!$C$6*Parametri!$C$7+U6*Parametri!$C$6*Parametri!$C$8+V6*Parametri!$C$6*Parametri!$C$9</f>
+        <v/>
+      </c>
+      <c r="AA6" s="9" t="inlineStr">
+        <is>
+          <t>Offerta § 6.1 — 90 minuti, remoto. Il contratto indica 2 risorse Impresoft (PM + RevOps Consultant): qui sono 3 per scelta di pianificazione. L'analisi dati non è un momento erogato al cliente: è back office dentro questa fase. gg back office: STIMA, non desunta dal contratto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="96" customHeight="1">
       <c r="A7" s="8" t="n">
         <v>2</v>
       </c>
@@ -1125,26 +1146,26 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Analisi dati e sintesi</t>
+          <t>Workshop #1 — Revenue model B2B e B2C</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Interna</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Interna</t>
+          <t>In presenza</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>1 · Avvio</t>
+          <t>2 · Workshop</t>
         </is>
       </c>
       <c r="G7" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" s="11" t="n">
         <v>1</v>
@@ -1155,27 +1176,27 @@
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>Analisi degli export ricevuti per ricostruire l'evidenza sulla base clienti attuale, su due piani: lettura logico-funzionale del dato e verifica di data quality. L'esito confluisce in una restituzione interna al team, in cui si presentano le evidenze emerse, l'issue tree e le prime ipotesi da validare nel corso del progetto.</t>
+          <t>Workshop in presenza per mappare le modalità con cui Laica genera valore sul canale B2B (distribuzione e OEM) e sui canali digitali B2C. Si analizza la proposta di valore per segmento, si mappano i canali di vendita e si esamina la struttura dei ricavi tra vendita dell'hardware e prodotti consumabili, costruendo il Revenue Model completo: value proposition, segmenti di clientela, competitor, canali, attività e risorse chiave, fonti di ricavo core, up-selling e cross-selling.</t>
         </is>
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
-          <t>Verifica di completezza e leggibilità degli export ricevuti.</t>
+          <t>Predisposizione del framework Revenue Model e condivisione dell'agenda.</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>Formalizzazione al cliente via email di dubbi, lacune e richieste di integrazione dati.</t>
+          <t>Compilazione del file di delivery, formalizzazione della mappa e restituzione al cliente; registrazione delle evidenze emerse.</t>
         </is>
       </c>
       <c r="M7" s="9" t="inlineStr">
         <is>
-          <t>Export dati completi e leggibili.</t>
+          <t>Disponibilità dei referenti di canale; dati di ricavo per linea di prodotto e per canale.</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>Evidenze sulla base clienti · esiti di data quality · issue tree · ipotesi da validare · lista domande al cliente.</t>
+          <t>Mappa formale del Revenue Model articolata per il canale B2B OEM e per i canali B2C.</t>
         </is>
       </c>
       <c r="O7" s="9" t="inlineStr">
@@ -1185,42 +1206,53 @@
       </c>
       <c r="P7" s="9" t="inlineStr">
         <is>
-          <t>1 consulente RevOps sull'analisi; restituzione di 1 ora all'intero team</t>
+          <t>Impresoft: 3 persone. Laica: Managing Director, Marketing Manager, CFO, CSO.</t>
         </is>
       </c>
       <c r="Q7" s="11" t="n">
         <v>1</v>
       </c>
       <c r="R7" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" s="13" t="n"/>
-      <c r="T7" s="13" t="n"/>
-      <c r="U7" s="13" t="n"/>
-      <c r="V7" s="9" t="inlineStr">
-        <is>
-          <t>1 risorsa in back office; restituzione al team di 1 ora con tutto il gruppo</t>
-        </is>
-      </c>
-      <c r="W7" s="14">
-        <f>IF(COUNT(S7:U7)=0,"",SUM(S7:U7))</f>
-        <v/>
+        <v>6</v>
+      </c>
+      <c r="S7" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" s="14">
+        <f>IF(OR(Q7="",R7="",S7=""),0,Q7*R7*S7/Parametri!$C$6)</f>
+        <v/>
+      </c>
+      <c r="U7" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V7" s="14">
+        <f>IF(AND(E7="In presenza",Q7&lt;&gt;"",S7&lt;&gt;""),Q7*S7*Parametri!$C$10/Parametri!$C$6,0)</f>
+        <v/>
+      </c>
+      <c r="W7" s="9" t="inlineStr">
+        <is>
+          <t>3 persone in presenza (1 facilitatore senior + 2 RevOps Consultant junior)</t>
+        </is>
       </c>
       <c r="X7" s="14">
-        <f>IF(W7="","",W7*Parametri!$C$5)</f>
-        <v/>
-      </c>
-      <c r="Y7" s="15">
-        <f>IF(COUNT(S7:U7)=0,"",S7*Parametri!$C$5*Parametri!$C$6+T7*Parametri!$C$5*Parametri!$C$7+U7*Parametri!$C$5*Parametri!$C$8)</f>
-        <v/>
-      </c>
-      <c r="Z7" s="9" t="inlineStr">
-        <is>
-          <t>L'analisi è svolta da una sola persona: la restituzione è l'unico momento collegiale.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="78" customHeight="1">
+        <f>T7+U7+V7</f>
+        <v/>
+      </c>
+      <c r="Y7" s="14">
+        <f>X7*Parametri!$C$6</f>
+        <v/>
+      </c>
+      <c r="Z7" s="15">
+        <f>T7*Parametri!$C$6*Parametri!$C$7+U7*Parametri!$C$6*Parametri!$C$8+V7*Parametri!$C$6*Parametri!$C$9</f>
+        <v/>
+      </c>
+      <c r="AA7" s="9" t="inlineStr">
+        <is>
+          <t>Offerta § 6.2 — 6 ore, in presenza, UN SOLO incontro per entrambi i canali. gg back office: STIMA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="96" customHeight="1">
       <c r="A8" s="8" t="n">
         <v>3</v>
       </c>
@@ -1231,7 +1263,7 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Revenue model</t>
+          <t>Workshop #2 — ICP, target group e customer journey</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -1246,11 +1278,11 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>2 · Workshop in parallelo</t>
+          <t>2 · Workshop</t>
         </is>
       </c>
       <c r="G8" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" s="11" t="n">
         <v>2</v>
@@ -1261,27 +1293,27 @@
       </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
-          <t>Workshop in presenza per la mappatura del modello di ricavo del cliente, articolato in due sessioni distinte — una dedicata al canale B2B e una al B2C — con compilazione congiunta del framework revenue model.</t>
+          <t>Due sessioni in presenza — una dedicata al B2B/OEM e una al B2C/D2C — per definire i profili di cliente target e ricostruire il percorso d'acquisto nei mercati di riferimento. L'Ideal Customer Profile è costruito con metodologia SPICED; il customer journey è mappato lungo le fasi di acquisizione ed espansione del bowtie (consapevolezza, educazione, vendita, onboarding, soddisfazione, espansione), con la mappatura B2C estesa ai touchpoint proprietari e ai marketplace.</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>Predisposizione dei materiali di workshop e condivisione dell'agenda con il cliente.</t>
+          <t>Predisposizione delle schede ICP e della struttura di journey; condivisione dell'agenda delle due sessioni.</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>Compilazione del file di delivery · restituzione formalizzata al cliente · registrazione delle evidenze emerse.</t>
+          <t>Compilazione del file di delivery, formalizzazione delle schede e della mappa, restituzione al cliente; registrazione delle evidenze emerse.</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
-          <t>Disponibilità dei referenti di canale e accesso ai dati di ricavo.</t>
+          <t>Disponibilità dei referenti marketing e sales per entrambe le sessioni.</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
-          <t>Revenue model mappato e validato per canale B2B e B2C.</t>
+          <t>Schede ICP B2B e B2C per segmento · mappa dettagliata del Customer Journey multicanale.</t>
         </is>
       </c>
       <c r="O8" s="9" t="inlineStr">
@@ -1291,40 +1323,53 @@
       </c>
       <c r="P8" s="9" t="inlineStr">
         <is>
-          <t>Facilitatore senior + 2 consulenti RevOps junior</t>
+          <t>Impresoft: 3 persone. Laica: Managing Director, Marketing Manager, CFO, CSO.</t>
         </is>
       </c>
       <c r="Q8" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="R8" s="13" t="n"/>
-      <c r="S8" s="13" t="n"/>
-      <c r="T8" s="13" t="n"/>
-      <c r="U8" s="13" t="n"/>
-      <c r="V8" s="9" t="inlineStr">
-        <is>
-          <t>3 persone in presenza (1 facilitatore senior + 2 consulenti junior)</t>
-        </is>
-      </c>
-      <c r="W8" s="14">
-        <f>IF(COUNT(S8:U8)=0,"",SUM(S8:U8))</f>
-        <v/>
+      <c r="R8" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="S8" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" s="14">
+        <f>IF(OR(Q8="",R8="",S8=""),0,Q8*R8*S8/Parametri!$C$6)</f>
+        <v/>
+      </c>
+      <c r="U8" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" s="14">
+        <f>IF(AND(E8="In presenza",Q8&lt;&gt;"",S8&lt;&gt;""),Q8*S8*Parametri!$C$10/Parametri!$C$6,0)</f>
+        <v/>
+      </c>
+      <c r="W8" s="9" t="inlineStr">
+        <is>
+          <t>3 persone in presenza × 2 sessioni (1 facilitatore senior + 2 RevOps Consultant junior)</t>
+        </is>
       </c>
       <c r="X8" s="14">
-        <f>IF(W8="","",W8*Parametri!$C$5)</f>
-        <v/>
-      </c>
-      <c r="Y8" s="15">
-        <f>IF(COUNT(S8:U8)=0,"",S8*Parametri!$C$5*Parametri!$C$6+T8*Parametri!$C$5*Parametri!$C$7+U8*Parametri!$C$5*Parametri!$C$8)</f>
-        <v/>
-      </c>
-      <c r="Z8" s="9" t="inlineStr">
-        <is>
-          <t>Durata delle due sessioni da definire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="78" customHeight="1">
+        <f>T8+U8+V8</f>
+        <v/>
+      </c>
+      <c r="Y8" s="14">
+        <f>X8*Parametri!$C$6</f>
+        <v/>
+      </c>
+      <c r="Z8" s="15">
+        <f>T8*Parametri!$C$6*Parametri!$C$7+U8*Parametri!$C$6*Parametri!$C$8+V8*Parametri!$C$6*Parametri!$C$9</f>
+        <v/>
+      </c>
+      <c r="AA8" s="9" t="inlineStr">
+        <is>
+          <t>Offerta § 6.3 — 12 ore complessive: 2 workshop dedicati (B2B + B2C) di circa 6 ore ciascuno, in presenza. È la fase più pesante del progetto. gg back office: STIMA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="96" customHeight="1">
       <c r="A9" s="8" t="n">
         <v>4</v>
       </c>
@@ -1335,7 +1380,7 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>ICP model e customer journey</t>
+          <t>Workshop #3 — Process design</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -1345,19 +1390,19 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>In presenza</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>2 · Workshop in parallelo</t>
+          <t>2 · Workshop</t>
         </is>
       </c>
       <c r="G9" s="11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" s="12">
         <f>IF(AND(G9&lt;&gt;"",H9&lt;&gt;""),G9+H9-1,"")</f>
@@ -1365,27 +1410,27 @@
       </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
-          <t>Due incontri in remoto — uno sul canale B2B e uno sul B2C — per la definizione del profilo di cliente ideale e della relativa customer journey. La mappatura si sviluppa sul bow tie: per ciascuna fase si individua il percorso desiderato e le frizioni oggi presenti.</t>
+          <t>Workshop in presenza per mappare i flussi operativi correnti tra i dipartimenti: processi di Marketing, Sales, Service e Operations, con i relativi flussi e frizioni as-is. Si rileva cosa funziona e cosa non funziona nei processi in essere e si identificano i gap rispetto allo stato desiderato definito nel customer journey.</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
-          <t>Predisposizione della struttura bow tie e condivisione dell'agenda.</t>
+          <t>Raccolta della documentazione di processo esistente; condivisione dell'agenda.</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>Compilazione del file di delivery · restituzione formalizzata al cliente · registrazione delle evidenze emerse.</t>
+          <t>Compilazione del file di delivery; avvio del diagramma dei flussi di processo as-is.</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
-          <t>Disponibilità dei referenti marketing e sales.</t>
+          <t>Documentazione di processo; disponibilità dei process owner.</t>
         </is>
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>Ideal Customer Profile definito · customer journey mappata lungo il bow tie con le frizioni per fase.</t>
+          <t>Diagramma dei flussi di processo as-is — contributo del workshop alla gap analysis.</t>
         </is>
       </c>
       <c r="O9" s="9" t="inlineStr">
@@ -1395,40 +1440,53 @@
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>Facilitatore senior + 2 consulenti RevOps junior</t>
+          <t>Impresoft: 3 persone. Laica: Marketing Manager, CSO, referente servizio clienti, key user operativi.</t>
         </is>
       </c>
       <c r="Q9" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="S9" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" s="14">
+        <f>IF(OR(Q9="",R9="",S9=""),0,Q9*R9*S9/Parametri!$C$6)</f>
+        <v/>
+      </c>
+      <c r="U9" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="R9" s="13" t="n"/>
-      <c r="S9" s="13" t="n"/>
-      <c r="T9" s="13" t="n"/>
-      <c r="U9" s="13" t="n"/>
-      <c r="V9" s="9" t="inlineStr">
-        <is>
-          <t>3 persone in remoto (1 facilitatore senior + 2 consulenti junior)</t>
-        </is>
-      </c>
-      <c r="W9" s="14">
-        <f>IF(COUNT(S9:U9)=0,"",SUM(S9:U9))</f>
-        <v/>
+      <c r="V9" s="14">
+        <f>IF(AND(E9="In presenza",Q9&lt;&gt;"",S9&lt;&gt;""),Q9*S9*Parametri!$C$10/Parametri!$C$6,0)</f>
+        <v/>
+      </c>
+      <c r="W9" s="9" t="inlineStr">
+        <is>
+          <t>3 persone in presenza (1 facilitatore senior + 2 RevOps Consultant junior)</t>
+        </is>
       </c>
       <c r="X9" s="14">
-        <f>IF(W9="","",W9*Parametri!$C$5)</f>
-        <v/>
-      </c>
-      <c r="Y9" s="15">
-        <f>IF(COUNT(S9:U9)=0,"",S9*Parametri!$C$5*Parametri!$C$6+T9*Parametri!$C$5*Parametri!$C$7+U9*Parametri!$C$5*Parametri!$C$8)</f>
-        <v/>
-      </c>
-      <c r="Z9" s="9" t="inlineStr">
-        <is>
-          <t>Durata delle due sessioni da definire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="78" customHeight="1">
+        <f>T9+U9+V9</f>
+        <v/>
+      </c>
+      <c r="Y9" s="14">
+        <f>X9*Parametri!$C$6</f>
+        <v/>
+      </c>
+      <c r="Z9" s="15">
+        <f>T9*Parametri!$C$6*Parametri!$C$7+U9*Parametri!$C$6*Parametri!$C$8+V9*Parametri!$C$6*Parametri!$C$9</f>
+        <v/>
+      </c>
+      <c r="AA9" s="9" t="inlineStr">
+        <is>
+          <t>Offerta § 6.4 — 6 ore, in presenza. Il perimetro contrattuale copre Marketing, Sales, Service e Operations. Nel contratto process design e user research sono un unico workshop: le interviste sono tenute su una riga a parte per separare i blocchi di progetto. gg back office: STIMA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="96" customHeight="1">
       <c r="A10" s="8" t="n">
         <v>5</v>
       </c>
@@ -1439,7 +1497,7 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Process design</t>
+          <t>Interviste one-to-one — user research</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -1449,19 +1507,19 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>In presenza</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>2 · Workshop in parallelo</t>
+          <t>3 · User research</t>
         </is>
       </c>
       <c r="G10" s="11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" s="12">
         <f>IF(AND(G10&lt;&gt;"",H10&lt;&gt;""),G10+H10-1,"")</f>
@@ -1469,27 +1527,27 @@
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
-          <t>Workshop in presenza per la mappatura dei processi attualmente in essere su marketing, sales e delivery. Si analizza cosa funziona e cosa non funziona nei flussi correnti e si individuano i gap rispetto allo stato desiderato definito nella customer journey.</t>
+          <t>Cinque interviste individuali alle persone chiave di sales, marketing e customer care, condotte a valle del process design da un solo consulente. Sono interviste qualitative volte a raccogliere insight su come i processi sono vissuti quotidianamente e a far emergere le frizioni operative e tecnologiche che la mappatura di processo non rende visibili.</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>Raccolta della documentazione di processo esistente e condivisione dell'agenda.</t>
+          <t>Selezione degli intervistati con il cliente; predisposizione della guida di intervista.</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>Compilazione del file di delivery · restituzione formalizzata al cliente · registrazione delle evidenze emerse.</t>
+          <t>Sintesi trasversale delle interviste e integrazione nel documento di gap analysis.</t>
         </is>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>Documentazione di processo e disponibilità dei process owner.</t>
+          <t>Individuazione e disponibilità delle 5 persone chiave da intervistare.</t>
         </is>
       </c>
       <c r="N10" s="9" t="inlineStr">
         <is>
-          <t>Mappatura del flusso di processo lungo l'intera catena del valore go-to-market · gap rispetto allo stato desiderato.</t>
+          <t>Insight qualitativi · documento di sintesi dei punti di attrito operativi (gap analysis).</t>
         </is>
       </c>
       <c r="O10" s="9" t="inlineStr">
@@ -1499,38 +1557,53 @@
       </c>
       <c r="P10" s="9" t="inlineStr">
         <is>
-          <t>Facilitatore senior + 2 consulenti RevOps junior</t>
-        </is>
-      </c>
-      <c r="Q10" s="11" t="n"/>
-      <c r="R10" s="13" t="n"/>
-      <c r="S10" s="13" t="n"/>
-      <c r="T10" s="13" t="n"/>
-      <c r="U10" s="13" t="n"/>
-      <c r="V10" s="9" t="inlineStr">
-        <is>
-          <t>3 persone in presenza (1 facilitatore senior + 2 consulenti junior)</t>
-        </is>
-      </c>
-      <c r="W10" s="14">
-        <f>IF(COUNT(S10:U10)=0,"",SUM(S10:U10))</f>
-        <v/>
+          <t>Impresoft: 1 RevOps Consultant junior. Laica: 5 persone chiave di sales, marketing e customer care.</t>
+        </is>
+      </c>
+      <c r="Q10" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" s="14">
+        <f>IF(OR(Q10="",R10="",S10=""),0,Q10*R10*S10/Parametri!$C$6)</f>
+        <v/>
+      </c>
+      <c r="U10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="14">
+        <f>IF(AND(E10="In presenza",Q10&lt;&gt;"",S10&lt;&gt;""),Q10*S10*Parametri!$C$10/Parametri!$C$6,0)</f>
+        <v/>
+      </c>
+      <c r="W10" s="9" t="inlineStr">
+        <is>
+          <t>1 persona in remoto (1 RevOps Consultant junior)</t>
+        </is>
       </c>
       <c r="X10" s="14">
-        <f>IF(W10="","",W10*Parametri!$C$5)</f>
-        <v/>
-      </c>
-      <c r="Y10" s="15">
-        <f>IF(COUNT(S10:U10)=0,"",S10*Parametri!$C$5*Parametri!$C$6+T10*Parametri!$C$5*Parametri!$C$7+U10*Parametri!$C$5*Parametri!$C$8)</f>
-        <v/>
-      </c>
-      <c r="Z10" s="9" t="inlineStr">
-        <is>
-          <t>Numero e durata delle sessioni da definire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="78" customHeight="1">
+        <f>T10+U10+V10</f>
+        <v/>
+      </c>
+      <c r="Y10" s="14">
+        <f>X10*Parametri!$C$6</f>
+        <v/>
+      </c>
+      <c r="Z10" s="15">
+        <f>T10*Parametri!$C$6*Parametri!$C$7+U10*Parametri!$C$6*Parametri!$C$8+V10*Parametri!$C$6*Parametri!$C$9</f>
+        <v/>
+      </c>
+      <c r="AA10" s="9" t="inlineStr">
+        <is>
+          <t>Offerta § 6.4 — il contratto fissa 5 interviste one-to-one ma NON la loro durata: 1 ora ciascuna è una stima. Attività compresa nel Workshop #3, isolata qui come blocco a sé. gg back office: STIMA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="96" customHeight="1">
       <c r="A11" s="8" t="n">
         <v>6</v>
       </c>
@@ -1541,7 +1614,7 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Tech stack</t>
+          <t>Workshop #4 — Tech stack e data governance</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -1551,19 +1624,19 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>Da definire</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>2 · Workshop in parallelo</t>
+          <t>2 · Workshop</t>
         </is>
       </c>
       <c r="G11" s="11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" s="12">
         <f>IF(AND(G11&lt;&gt;"",H11&lt;&gt;""),G11+H11-1,"")</f>
@@ -1571,7 +1644,7 @@
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>Ricognizione degli strumenti oggi in uso che intercettano la strategia go-to-market, con verifica di come sono strutturati database e flussi di dati. L'obiettivo è fotografare lo stack as-is e disegnare lo stack to-be in ottica di razionalizzazione.</t>
+          <t>Sessione in remoto per mappare le applicazioni in uso che impattano i processi di go-to-market: CRM HubSpot, gestionale/ERP, e-commerce, connettori marketplace. Si individua dove risiede l'informazione, come i dati fluiscono tra i sistemi e si analizzano le integrazioni esistenti, con l'obiettivo di fotografare lo stack as-is.</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
@@ -1581,17 +1654,17 @@
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>Compilazione del file di delivery · restituzione formalizzata al cliente · registrazione delle evidenze emerse.</t>
+          <t>Compilazione del file di delivery; formalizzazione della mappa architetturale e degli schemi di integrazione.</t>
         </is>
       </c>
       <c r="M11" s="9" t="inlineStr">
         <is>
-          <t>Inventario degli strumenti in uso e accesso ai referenti IT.</t>
+          <t>Inventario degli strumenti in uso; accesso ai referenti IT e, se necessario, ai fornitori software esterni.</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>Mappa degli strumenti as-is e to-be · indicazioni di razionalizzazione dello stack e del database.</t>
+          <t>Mappa dell'architettura applicativa corrente · schema dei flussi di integrazione dati.</t>
         </is>
       </c>
       <c r="O11" s="9" t="inlineStr">
@@ -1601,38 +1674,53 @@
       </c>
       <c r="P11" s="9" t="inlineStr">
         <is>
-          <t>Facilitatore senior + 2 consulenti RevOps junior</t>
-        </is>
-      </c>
-      <c r="Q11" s="11" t="n"/>
-      <c r="R11" s="13" t="n"/>
-      <c r="S11" s="13" t="n"/>
-      <c r="T11" s="13" t="n"/>
-      <c r="U11" s="13" t="n"/>
-      <c r="V11" s="9" t="inlineStr">
-        <is>
-          <t>3 persone (1 facilitatore senior + 2 consulenti junior)</t>
-        </is>
-      </c>
-      <c r="W11" s="14">
-        <f>IF(COUNT(S11:U11)=0,"",SUM(S11:U11))</f>
-        <v/>
+          <t>Impresoft: 3 persone. Laica: referenti IT / sistemi informativi, key user di processo, eventuali fornitori software esterni.</t>
+        </is>
+      </c>
+      <c r="Q11" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="S11" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" s="14">
+        <f>IF(OR(Q11="",R11="",S11=""),0,Q11*R11*S11/Parametri!$C$6)</f>
+        <v/>
+      </c>
+      <c r="U11" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" s="14">
+        <f>IF(AND(E11="In presenza",Q11&lt;&gt;"",S11&lt;&gt;""),Q11*S11*Parametri!$C$10/Parametri!$C$6,0)</f>
+        <v/>
+      </c>
+      <c r="W11" s="9" t="inlineStr">
+        <is>
+          <t>3 persone in remoto (1 facilitatore senior + 2 RevOps Consultant junior)</t>
+        </is>
       </c>
       <c r="X11" s="14">
-        <f>IF(W11="","",W11*Parametri!$C$5)</f>
-        <v/>
-      </c>
-      <c r="Y11" s="15">
-        <f>IF(COUNT(S11:U11)=0,"",S11*Parametri!$C$5*Parametri!$C$6+T11*Parametri!$C$5*Parametri!$C$7+U11*Parametri!$C$5*Parametri!$C$8)</f>
-        <v/>
-      </c>
-      <c r="Z11" s="9" t="inlineStr">
-        <is>
-          <t>Modalità (presenza / remoto), numero e durata delle sessioni da definire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="78" customHeight="1">
+        <f>T11+U11+V11</f>
+        <v/>
+      </c>
+      <c r="Y11" s="14">
+        <f>X11*Parametri!$C$6</f>
+        <v/>
+      </c>
+      <c r="Z11" s="15">
+        <f>T11*Parametri!$C$6*Parametri!$C$7+U11*Parametri!$C$6*Parametri!$C$8+V11*Parametri!$C$6*Parametri!$C$9</f>
+        <v/>
+      </c>
+      <c r="AA11" s="9" t="inlineStr">
+        <is>
+          <t>Offerta § 6.5 — 4 ore, in remoto. gg back office: STIMA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="96" customHeight="1">
       <c r="A12" s="8" t="n">
         <v>7</v>
       </c>
@@ -1643,7 +1731,7 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Data model</t>
+          <t>Workshop #5 — Data model e prioritizzazione</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -1653,19 +1741,19 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Da definire</t>
+          <t>In presenza</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>2 · Workshop in parallelo</t>
+          <t>2 · Workshop</t>
         </is>
       </c>
       <c r="G12" s="11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" s="12">
         <f>IF(AND(G12&lt;&gt;"",H12&lt;&gt;""),G12+H12-1,"")</f>
@@ -1673,17 +1761,17 @@
       </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
-          <t>Incontro dedicato alla proposta del set di KPI necessari a misurare il sistema, costruito utilizzando il bow tie come backbone. Si definiscono KPI di primo e di secondo livello per monitorare l'avanzamento della generazione di valore.</t>
+          <t>Workshop in presenza per definire la struttura dei dati target — modello dati unificato per la gestione di cliente e prodotto — individuando i dati da tracciare lungo il customer journey, i KPI e i criteri di transizione. Nella seconda parte si consolidano le attività emerse e si prioritizzano per impatto, velocità a impatto e semplicità, classificandole con matrice di priorità.</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>Predisposizione dell'albero dei KPI di primo e secondo livello sul bow tie.</t>
+          <t>Predisposizione dell'albero dei KPI sul bowtie e della matrice di prioritizzazione.</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>Compilazione del file di delivery · restituzione formalizzata al cliente · registrazione delle evidenze emerse.</t>
+          <t>Formalizzazione del Data Model target; consolidamento delle priorità in vista della roadmap.</t>
         </is>
       </c>
       <c r="M12" s="9" t="inlineStr">
@@ -1693,7 +1781,7 @@
       </c>
       <c r="N12" s="9" t="inlineStr">
         <is>
-          <t>Set di KPI di primo e secondo livello ancorati al bow tie · logica di misurazione della generazione di valore.</t>
+          <t>Data Model target · classificazione degli interventi per matrice di priorità.</t>
         </is>
       </c>
       <c r="O12" s="9" t="inlineStr">
@@ -1703,40 +1791,53 @@
       </c>
       <c r="P12" s="9" t="inlineStr">
         <is>
-          <t>Facilitatore senior + 2 consulenti RevOps junior</t>
+          <t>Impresoft: 3 persone. Laica: Managing Director, Marketing Manager, CFO, CSO, referente IT.</t>
         </is>
       </c>
       <c r="Q12" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="R12" s="13" t="n"/>
-      <c r="S12" s="13" t="n"/>
-      <c r="T12" s="13" t="n"/>
-      <c r="U12" s="13" t="n"/>
-      <c r="V12" s="9" t="inlineStr">
-        <is>
-          <t>3 persone (1 facilitatore senior + 2 consulenti junior)</t>
-        </is>
-      </c>
-      <c r="W12" s="14">
-        <f>IF(COUNT(S12:U12)=0,"",SUM(S12:U12))</f>
-        <v/>
+      <c r="R12" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="S12" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" s="14">
+        <f>IF(OR(Q12="",R12="",S12=""),0,Q12*R12*S12/Parametri!$C$6)</f>
+        <v/>
+      </c>
+      <c r="U12" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V12" s="14">
+        <f>IF(AND(E12="In presenza",Q12&lt;&gt;"",S12&lt;&gt;""),Q12*S12*Parametri!$C$10/Parametri!$C$6,0)</f>
+        <v/>
+      </c>
+      <c r="W12" s="9" t="inlineStr">
+        <is>
+          <t>3 persone in presenza (1 facilitatore senior + 2 RevOps Consultant junior)</t>
+        </is>
       </c>
       <c r="X12" s="14">
-        <f>IF(W12="","",W12*Parametri!$C$5)</f>
-        <v/>
-      </c>
-      <c r="Y12" s="15">
-        <f>IF(COUNT(S12:U12)=0,"",S12*Parametri!$C$5*Parametri!$C$6+T12*Parametri!$C$5*Parametri!$C$7+U12*Parametri!$C$5*Parametri!$C$8)</f>
-        <v/>
-      </c>
-      <c r="Z12" s="9" t="inlineStr">
-        <is>
-          <t>Modalità (presenza / remoto) e durata da definire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="78" customHeight="1">
+        <f>T12+U12+V12</f>
+        <v/>
+      </c>
+      <c r="Y12" s="14">
+        <f>X12*Parametri!$C$6</f>
+        <v/>
+      </c>
+      <c r="Z12" s="15">
+        <f>T12*Parametri!$C$6*Parametri!$C$7+U12*Parametri!$C$6*Parametri!$C$8+V12*Parametri!$C$6*Parametri!$C$9</f>
+        <v/>
+      </c>
+      <c r="AA12" s="9" t="inlineStr">
+        <is>
+          <t>Offerta § 6.6 — 6 ore, in presenza. Il contratto indica 4 risorse Impresoft sul § 6.6 (RevOps Consultant, CX Specialist, Integration Expert, PM): qui sono 3. La roadmap per wave non è una fase: è contenuto del report finale. gg back office: STIMA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="96" customHeight="1">
       <c r="A13" s="8" t="n">
         <v>8</v>
       </c>
@@ -1747,7 +1848,7 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Interviste qualitative</t>
+          <t>Review con il cliente</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -1762,11 +1863,11 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>3 · Approfondimento</t>
+          <t>4 · Sintesi e validazione</t>
         </is>
       </c>
       <c r="G13" s="11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H13" s="11" t="n">
         <v>1</v>
@@ -1777,27 +1878,27 @@
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>Ciclo di interviste individuali in remoto, condotte da un solo consulente a valle del process design. Sono interviste qualitative volte a raccogliere il punto di vista degli utenti interni sui temi emersi nei workshop e a far emergere frizioni operative non visibili nella mappatura di processo.</t>
+          <t>Incontro di validazione con il team di lavoro lato cliente sui business case e sulle priorità consolidate, prima della formalizzazione del report. Si verifica l'allineamento su priorità e numeri e si stabilisce se procedere o iterare su specifici ambiti.</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>Selezione degli intervistati con il cliente e predisposizione della guida di intervista.</t>
+          <t>Invio anticipato dei business case e della matrice di priorità per lettura preventiva.</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>Sintesi trasversale delle interviste e integrazione delle frizioni nella mappatura di processo.</t>
+          <t>Recepimento delle iterazioni richieste e aggiornamento del report in costruzione.</t>
         </is>
       </c>
       <c r="M13" s="9" t="inlineStr">
         <is>
-          <t>Individuazione e disponibilità degli utenti interni da intervistare.</t>
+          <t>Presenza dei decisori lato cliente.</t>
         </is>
       </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
-          <t>Frizioni operative rilevate · feedback qualitativi sui temi aperti nel process design.</t>
+          <t>Business case e priorità validati, oppure lista delle iterazioni richieste.</t>
         </is>
       </c>
       <c r="O13" s="9" t="inlineStr">
@@ -1807,38 +1908,51 @@
       </c>
       <c r="P13" s="9" t="inlineStr">
         <is>
-          <t>1 consulente RevOps; referenti operativi lato cliente</t>
-        </is>
-      </c>
-      <c r="Q13" s="11" t="n"/>
+          <t>Impresoft: 3 persone. Laica: team di lavoro e decisori.</t>
+        </is>
+      </c>
+      <c r="Q13" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="R13" s="13" t="n"/>
-      <c r="S13" s="13" t="n"/>
-      <c r="T13" s="13" t="n"/>
-      <c r="U13" s="13" t="n"/>
-      <c r="V13" s="9" t="inlineStr">
-        <is>
-          <t>1 persona in remoto</t>
-        </is>
-      </c>
-      <c r="W13" s="14">
-        <f>IF(COUNT(S13:U13)=0,"",SUM(S13:U13))</f>
-        <v/>
+      <c r="S13" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" s="14">
+        <f>IF(OR(Q13="",R13="",S13=""),0,Q13*R13*S13/Parametri!$C$6)</f>
+        <v/>
+      </c>
+      <c r="U13" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V13" s="14">
+        <f>IF(AND(E13="In presenza",Q13&lt;&gt;"",S13&lt;&gt;""),Q13*S13*Parametri!$C$10/Parametri!$C$6,0)</f>
+        <v/>
+      </c>
+      <c r="W13" s="9" t="inlineStr">
+        <is>
+          <t>3 persone in remoto (1 facilitatore senior + 2 RevOps Consultant junior)</t>
+        </is>
       </c>
       <c r="X13" s="14">
-        <f>IF(W13="","",W13*Parametri!$C$5)</f>
-        <v/>
-      </c>
-      <c r="Y13" s="15">
-        <f>IF(COUNT(S13:U13)=0,"",S13*Parametri!$C$5*Parametri!$C$6+T13*Parametri!$C$5*Parametri!$C$7+U13*Parametri!$C$5*Parametri!$C$8)</f>
-        <v/>
-      </c>
-      <c r="Z13" s="9" t="inlineStr">
-        <is>
-          <t>Fase separata perché si svolge a valle dei workshop, con un solo consulente impegnato.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="78" customHeight="1">
+        <f>T13+U13+V13</f>
+        <v/>
+      </c>
+      <c r="Y13" s="14">
+        <f>X13*Parametri!$C$6</f>
+        <v/>
+      </c>
+      <c r="Z13" s="15">
+        <f>T13*Parametri!$C$6*Parametri!$C$7+U13*Parametri!$C$6*Parametri!$C$8+V13*Parametri!$C$6*Parametri!$C$9</f>
+        <v/>
+      </c>
+      <c r="AA13" s="9" t="inlineStr">
+        <is>
+          <t>FUORI PERIMETRO CONTRATTUALE — l'Offerta non prevede una sessione di review tra il Workshop #5 e il meeting di presentazione. Mantenuta su richiesta. DURATA DA DEFINIRE: finché la cella è vuota le giornate front di questa fase valgono 0. gg back office: STIMA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="96" customHeight="1">
       <c r="A14" s="8" t="n">
         <v>9</v>
       </c>
@@ -1849,7 +1963,7 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Sintesi evidenze e business case</t>
+          <t>Consolidamento report, roadmap e business case</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -1868,10 +1982,10 @@
         </is>
       </c>
       <c r="G14" s="11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" s="12">
         <f>IF(AND(G14&lt;&gt;"",H14&lt;&gt;""),G14+H14-1,"")</f>
@@ -1879,23 +1993,23 @@
       </c>
       <c r="J14" s="9" t="inlineStr">
         <is>
-          <t>Fase interna di ristrutturazione di tutte le evidenze raccolte e di costruzione del piano di lavoro, con elaborazione dei business case a supporto delle iniziative individuate.</t>
+          <t>Fase interna di consolidamento dell'intero assessment: costruzione del report consolidato, della roadmap strategica di implementazione suddivisa per wave secondo le priorità individuate e del business case economico analitico a supporto. Il documento viene anticipato al cliente via e-mail in PDF prima del meeting di presentazione.</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>Consolidamento dei file di delivery di tutte le fasi precedenti.</t>
+          <t>Consolidamento dei file di delivery di tutte le sessioni precedenti e degli esiti della review.</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>Predisposizione dei materiali per la review con il cliente.</t>
+          <t>Invio anticipato del PDF al cliente in vista del meeting di presentazione.</t>
         </is>
       </c>
       <c r="M14" s="9" t="n"/>
       <c r="N14" s="9" t="inlineStr">
         <is>
-          <t>Piano di lavoro strutturato · business case per iniziativa.</t>
+          <t>Report consolidato di assessment · roadmap per wave · business case economico · PDF in lingua italiana.</t>
         </is>
       </c>
       <c r="O14" s="9" t="inlineStr">
@@ -1910,25 +2024,38 @@
       </c>
       <c r="Q14" s="11" t="n"/>
       <c r="R14" s="13" t="n"/>
-      <c r="S14" s="13" t="n"/>
-      <c r="T14" s="13" t="n"/>
-      <c r="U14" s="13" t="n"/>
-      <c r="V14" s="9" t="n"/>
-      <c r="W14" s="14">
-        <f>IF(COUNT(S14:U14)=0,"",SUM(S14:U14))</f>
-        <v/>
-      </c>
+      <c r="S14" s="11" t="n"/>
+      <c r="T14" s="14">
+        <f>IF(OR(Q14="",R14="",S14=""),0,Q14*R14*S14/Parametri!$C$6)</f>
+        <v/>
+      </c>
+      <c r="U14" s="13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V14" s="14">
+        <f>IF(AND(E14="In presenza",Q14&lt;&gt;"",S14&lt;&gt;""),Q14*S14*Parametri!$C$10/Parametri!$C$6,0)</f>
+        <v/>
+      </c>
+      <c r="W14" s="9" t="n"/>
       <c r="X14" s="14">
-        <f>IF(W14="","",W14*Parametri!$C$5)</f>
-        <v/>
-      </c>
-      <c r="Y14" s="15">
-        <f>IF(COUNT(S14:U14)=0,"",S14*Parametri!$C$5*Parametri!$C$6+T14*Parametri!$C$5*Parametri!$C$7+U14*Parametri!$C$5*Parametri!$C$8)</f>
-        <v/>
-      </c>
-      <c r="Z14" s="9" t="n"/>
-    </row>
-    <row r="15" ht="78" customHeight="1">
+        <f>T14+U14+V14</f>
+        <v/>
+      </c>
+      <c r="Y14" s="14">
+        <f>X14*Parametri!$C$6</f>
+        <v/>
+      </c>
+      <c r="Z14" s="15">
+        <f>T14*Parametri!$C$6*Parametri!$C$7+U14*Parametri!$C$6*Parametri!$C$8+V14*Parametri!$C$6*Parametri!$C$9</f>
+        <v/>
+      </c>
+      <c r="AA14" s="9" t="inlineStr">
+        <is>
+          <t>Offerta § 6.6 e § 11 — l'invio anticipato del PDF è la milestone che attiva la fatturazione del 50% residuo. gg back office: STIMA, ed è la voce più pesante del progetto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="96" customHeight="1">
       <c r="A15" s="8" t="n">
         <v>10</v>
       </c>
@@ -1939,7 +2066,7 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Review con il cliente</t>
+          <t>Meeting di presentazione dell'output</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -1949,16 +2076,16 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>In presenza</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>4 · Sintesi e validazione</t>
+          <t>5 · Chiusura</t>
         </is>
       </c>
       <c r="G15" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H15" s="11" t="n">
         <v>1</v>
@@ -1969,17 +2096,17 @@
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>Incontro di validazione con il team di lavoro lato cliente, centrato sui business case costruiti: si verifica l'allineamento su priorità e numeri e si stabilisce se procedere o iterare su specifici ambiti.</t>
+          <t>Presentazione in presenza dell'output finale dell'assessment — report consolidato, roadmap per wave e business case — come passaggio verso le successive scelte di investimento tecnologico e organizzativo. Si svolge circa 15 giorni dopo il workshop Data Model.</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>Invio anticipato dei business case per lettura preventiva.</t>
+          <t>Predisposizione delle slide di presentazione; conferma di agenda e partecipanti.</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>Recepimento delle iterazioni richieste e aggiornamento del piano di lavoro.</t>
+          <t>Raccolta delle precisazioni e micro-rettifiche emerse in incontro, da recepire nella versione inglese del report.</t>
         </is>
       </c>
       <c r="M15" s="9" t="inlineStr">
@@ -1989,7 +2116,7 @@
       </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>Business case validati oppure lista delle iterazioni richieste.</t>
+          <t>Assessment presentato e consegnato · next step condivisi.</t>
         </is>
       </c>
       <c r="O15" s="9" t="inlineStr">
@@ -1999,36 +2126,53 @@
       </c>
       <c r="P15" s="9" t="inlineStr">
         <is>
-          <t>Team di progetto + team di lavoro lato cliente</t>
+          <t>Impresoft: 3 persone. Laica: Managing Director, Marketing Manager, CFO, CSO, referente IT.</t>
         </is>
       </c>
       <c r="Q15" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="R15" s="13" t="n"/>
-      <c r="S15" s="13" t="n"/>
-      <c r="T15" s="13" t="n"/>
-      <c r="U15" s="13" t="n"/>
-      <c r="V15" s="9" t="n"/>
-      <c r="W15" s="14">
-        <f>IF(COUNT(S15:U15)=0,"",SUM(S15:U15))</f>
-        <v/>
+      <c r="R15" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" s="14">
+        <f>IF(OR(Q15="",R15="",S15=""),0,Q15*R15*S15/Parametri!$C$6)</f>
+        <v/>
+      </c>
+      <c r="U15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="14">
+        <f>IF(AND(E15="In presenza",Q15&lt;&gt;"",S15&lt;&gt;""),Q15*S15*Parametri!$C$10/Parametri!$C$6,0)</f>
+        <v/>
+      </c>
+      <c r="W15" s="9" t="inlineStr">
+        <is>
+          <t>3 persone in presenza (1 facilitatore senior + 2 RevOps Consultant junior)</t>
+        </is>
       </c>
       <c r="X15" s="14">
-        <f>IF(W15="","",W15*Parametri!$C$5)</f>
-        <v/>
-      </c>
-      <c r="Y15" s="15">
-        <f>IF(COUNT(S15:U15)=0,"",S15*Parametri!$C$5*Parametri!$C$6+T15*Parametri!$C$5*Parametri!$C$7+U15*Parametri!$C$5*Parametri!$C$8)</f>
-        <v/>
-      </c>
-      <c r="Z15" s="9" t="inlineStr">
-        <is>
-          <t>GATE DI PROGETTO: il consolidamento del report parte solo a validazione avvenuta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="78" customHeight="1">
+        <f>T15+U15+V15</f>
+        <v/>
+      </c>
+      <c r="Y15" s="14">
+        <f>X15*Parametri!$C$6</f>
+        <v/>
+      </c>
+      <c r="Z15" s="15">
+        <f>T15*Parametri!$C$6*Parametri!$C$7+U15*Parametri!$C$6*Parametri!$C$8+V15*Parametri!$C$6*Parametri!$C$9</f>
+        <v/>
+      </c>
+      <c r="AA15" s="9" t="inlineStr">
+        <is>
+          <t>Offerta § 6.6 — 2 ore, in presenza, circa 15 giorni dopo il Workshop #5. VINCOLO DI PIANIFICAZIONE da rispettare nella colonna «Sett. inizio». gg back office: STIMA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="96" customHeight="1">
       <c r="A16" s="8" t="n">
         <v>11</v>
       </c>
@@ -2039,7 +2183,7 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Consolidamento report finale</t>
+          <t>Redazione output in lingua inglese</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -2058,10 +2202,10 @@
         </is>
       </c>
       <c r="G16" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" s="12">
         <f>IF(AND(G16&lt;&gt;"",H16&lt;&gt;""),G16+H16-1,"")</f>
@@ -2069,23 +2213,23 @@
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>Consolidamento dell'intero assessment nel report finale: stesura delle slide in versione definitiva e valorizzazione economica della roadmap di progetto.</t>
+          <t>Redazione della versione inglese del report di assessment, che il contratto colloca esplicitamente dopo il meeting di presentazione per poter includere le precisazioni e le micro-rettifiche emerse durante l'incontro.</t>
         </is>
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>Recepimento degli esiti della review con il cliente.</t>
+          <t>Recepimento delle rettifiche emerse in presentazione.</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>Condivisione anticipata del report con i referenti prima della presentazione.</t>
+          <t>Consegna del PDF in lingua inglese.</t>
         </is>
       </c>
       <c r="M16" s="9" t="n"/>
       <c r="N16" s="9" t="inlineStr">
         <is>
-          <t>Report finale di assessment · roadmap di progetto valorizzata economicamente.</t>
+          <t>Report di assessment in lingua inglese (PDF).</t>
         </is>
       </c>
       <c r="O16" s="9" t="inlineStr">
@@ -2100,339 +2244,110 @@
       </c>
       <c r="Q16" s="11" t="n"/>
       <c r="R16" s="13" t="n"/>
-      <c r="S16" s="13" t="n"/>
-      <c r="T16" s="13" t="n"/>
-      <c r="U16" s="13" t="n"/>
-      <c r="V16" s="9" t="n"/>
-      <c r="W16" s="14">
-        <f>IF(COUNT(S16:U16)=0,"",SUM(S16:U16))</f>
-        <v/>
-      </c>
+      <c r="S16" s="11" t="n"/>
+      <c r="T16" s="14">
+        <f>IF(OR(Q16="",R16="",S16=""),0,Q16*R16*S16/Parametri!$C$6)</f>
+        <v/>
+      </c>
+      <c r="U16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="14">
+        <f>IF(AND(E16="In presenza",Q16&lt;&gt;"",S16&lt;&gt;""),Q16*S16*Parametri!$C$10/Parametri!$C$6,0)</f>
+        <v/>
+      </c>
+      <c r="W16" s="9" t="n"/>
       <c r="X16" s="14">
-        <f>IF(W16="","",W16*Parametri!$C$5)</f>
-        <v/>
-      </c>
-      <c r="Y16" s="15">
-        <f>IF(COUNT(S16:U16)=0,"",S16*Parametri!$C$5*Parametri!$C$6+T16*Parametri!$C$5*Parametri!$C$7+U16*Parametri!$C$5*Parametri!$C$8)</f>
-        <v/>
-      </c>
-      <c r="Z16" s="9" t="n"/>
-    </row>
-    <row r="17" ht="78" customHeight="1">
-      <c r="A17" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Presentazione assessment</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>Da definire</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>5 · Chiusura</t>
-        </is>
-      </c>
-      <c r="G17" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="H17" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="12">
-        <f>IF(AND(G17&lt;&gt;"",H17&lt;&gt;""),G17+H17-1,"")</f>
-        <v/>
-      </c>
-      <c r="J17" s="9" t="inlineStr">
-        <is>
-          <t>Presentazione al cliente del report finale di assessment, della roadmap e della relativa valorizzazione economica, come passaggio di consegna verso la fase successiva.</t>
-        </is>
-      </c>
-      <c r="K17" s="9" t="inlineStr">
-        <is>
-          <t>Allineamento sull'agenda e sui partecipanti lato cliente.</t>
-        </is>
-      </c>
-      <c r="L17" s="9" t="inlineStr">
-        <is>
-          <t>Consegna formale del report e apertura del confronto sulla fase successiva.</t>
-        </is>
-      </c>
-      <c r="M17" s="9" t="inlineStr">
-        <is>
-          <t>Presenza dei decisori lato cliente.</t>
-        </is>
-      </c>
-      <c r="N17" s="9" t="inlineStr">
-        <is>
-          <t>Assessment consegnato · roadmap valorizzata condivisa · next step definiti.</t>
-        </is>
-      </c>
-      <c r="O17" s="9" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
-      <c r="P17" s="9" t="inlineStr">
-        <is>
-          <t>Team di progetto + decisori lato cliente</t>
-        </is>
-      </c>
-      <c r="Q17" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" s="13" t="n"/>
-      <c r="S17" s="13" t="n"/>
-      <c r="T17" s="13" t="n"/>
-      <c r="U17" s="13" t="n"/>
-      <c r="V17" s="9" t="n"/>
-      <c r="W17" s="14">
-        <f>IF(COUNT(S17:U17)=0,"",SUM(S17:U17))</f>
-        <v/>
-      </c>
-      <c r="X17" s="14">
-        <f>IF(W17="","",W17*Parametri!$C$5)</f>
-        <v/>
-      </c>
-      <c r="Y17" s="15">
-        <f>IF(COUNT(S17:U17)=0,"",S17*Parametri!$C$5*Parametri!$C$6+T17*Parametri!$C$5*Parametri!$C$7+U17*Parametri!$C$5*Parametri!$C$8)</f>
-        <v/>
-      </c>
-      <c r="Z17" s="9" t="inlineStr">
-        <is>
-          <t>Modalità (presenza / remoto) da definire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+        <f>T16+U16+V16</f>
+        <v/>
+      </c>
+      <c r="Y16" s="14">
+        <f>X16*Parametri!$C$6</f>
+        <v/>
+      </c>
+      <c r="Z16" s="15">
+        <f>T16*Parametri!$C$6*Parametri!$C$7+U16*Parametri!$C$6*Parametri!$C$8+V16*Parametri!$C$6*Parametri!$C$9</f>
+        <v/>
+      </c>
+      <c r="AA16" s="9" t="inlineStr">
+        <is>
+          <t>Offerta § 6.6 — deliverable obbligatorio. ATTENZIONE: il § 6.7 esclude dall'offerta la «traduzione di testi» come servizio di terze parti, quindi la versione inglese è a carico interno. Questa coda cade OLTRE le 10 settimane dichiarate al § 8. gg back office: STIMA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>TOTALE PROGETTO</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="16" t="n"/>
-      <c r="H18" s="16" t="n"/>
-      <c r="I18" s="16" t="n"/>
-      <c r="J18" s="16" t="n"/>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="16" t="n"/>
-      <c r="M18" s="16" t="n"/>
-      <c r="N18" s="16" t="n"/>
-      <c r="O18" s="16" t="n"/>
-      <c r="P18" s="16" t="n"/>
-      <c r="Q18" s="17" t="n"/>
-      <c r="R18" s="16" t="n"/>
-      <c r="S18" s="18">
-        <f>SUM(S6:S17)</f>
-        <v/>
-      </c>
-      <c r="T18" s="18">
-        <f>SUM(T6:T17)</f>
-        <v/>
-      </c>
-      <c r="U18" s="18">
-        <f>SUM(U6:U17)</f>
-        <v/>
-      </c>
-      <c r="V18" s="16" t="n"/>
-      <c r="W18" s="18">
-        <f>SUM(W6:W17)</f>
-        <v/>
-      </c>
-      <c r="X18" s="18">
-        <f>SUM(X6:X17)</f>
-        <v/>
-      </c>
-      <c r="Y18" s="19">
-        <f>SUM(Y6:Y17)</f>
-        <v/>
-      </c>
-      <c r="Z18" s="16" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>ESEMPIO DI COMPILAZIONE — riga dimostrativa, NON conteggiata nei totali. Mostra il formato atteso per le colonne numeriche.</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="n"/>
-      <c r="C20" s="21" t="n"/>
-      <c r="D20" s="21" t="n"/>
-      <c r="E20" s="21" t="n"/>
-      <c r="F20" s="21" t="n"/>
-      <c r="G20" s="21" t="n"/>
-      <c r="H20" s="21" t="n"/>
-      <c r="I20" s="21" t="n"/>
-      <c r="J20" s="21" t="n"/>
-      <c r="K20" s="21" t="n"/>
-      <c r="L20" s="21" t="n"/>
-      <c r="M20" s="21" t="n"/>
-      <c r="N20" s="21" t="n"/>
-      <c r="O20" s="21" t="n"/>
-      <c r="P20" s="21" t="n"/>
-      <c r="Q20" s="21" t="n"/>
-      <c r="R20" s="21" t="n"/>
-      <c r="S20" s="21" t="n"/>
-      <c r="T20" s="21" t="n"/>
-      <c r="U20" s="21" t="n"/>
-      <c r="V20" s="21" t="n"/>
-      <c r="W20" s="21" t="n"/>
-      <c r="X20" s="21" t="n"/>
-      <c r="Y20" s="21" t="n"/>
-      <c r="Z20" s="21" t="n"/>
-    </row>
-    <row r="21" ht="44" customHeight="1">
-      <c r="A21" s="22" t="inlineStr">
-        <is>
-          <t>es.</t>
-        </is>
-      </c>
-      <c r="B21" s="23" t="inlineStr">
-        <is>
-          <t>1.x</t>
-        </is>
-      </c>
-      <c r="C21" s="23" t="inlineStr">
-        <is>
-          <t>Nome della fase</t>
-        </is>
-      </c>
-      <c r="D21" s="23" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="E21" s="23" t="inlineStr">
-        <is>
-          <t>In presenza</t>
-        </is>
-      </c>
-      <c r="F21" s="23" t="inlineStr">
-        <is>
-          <t>2 · Workshop in parallelo</t>
-        </is>
-      </c>
-      <c r="G21" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="H21" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" s="24">
-        <f>G21+H21-1</f>
-        <v/>
-      </c>
-      <c r="J21" s="23" t="inlineStr">
-        <is>
-          <t>Descrizione sintetica di cosa avviene nella fase.</t>
-        </is>
-      </c>
-      <c r="K21" s="23" t="inlineStr">
-        <is>
-          <t>Cosa si fa prima.</t>
-        </is>
-      </c>
-      <c r="L21" s="23" t="inlineStr">
-        <is>
-          <t>Cosa si fa dopo.</t>
-        </is>
-      </c>
-      <c r="M21" s="23" t="inlineStr">
-        <is>
-          <t>Cosa serve dal cliente.</t>
-        </is>
-      </c>
-      <c r="N21" s="23" t="inlineStr">
-        <is>
-          <t>Cosa esce dalla fase.</t>
-        </is>
-      </c>
-      <c r="O21" s="23" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
-      <c r="P21" s="23" t="inlineStr">
-        <is>
-          <t>Facilitatore senior + 2 consulenti junior</t>
-        </is>
-      </c>
-      <c r="Q21" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="R21" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="S21" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T21" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V21" s="23" t="inlineStr">
-        <is>
-          <t>3 persone in presenza, 1 sola lavora in back office</t>
-        </is>
-      </c>
-      <c r="W21" s="25">
-        <f>SUM(S21:U21)</f>
-        <v/>
-      </c>
-      <c r="X21" s="25">
-        <f>W21*Parametri!$C$5</f>
-        <v/>
-      </c>
-      <c r="Y21" s="26">
-        <f>S21*Parametri!$C$5*Parametri!$C$6+T21*Parametri!$C$5*Parametri!$C$7+U21*Parametri!$C$5*Parametri!$C$8</f>
-        <v/>
-      </c>
-      <c r="Z21" s="23" t="inlineStr">
-        <is>
-          <t>1,5 gg front = 3 consulenti per mezza giornata + 3 consulenti per mezza giornata.</t>
-        </is>
-      </c>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
+      <c r="G17" s="16" t="n"/>
+      <c r="H17" s="16" t="n"/>
+      <c r="I17" s="16" t="n"/>
+      <c r="J17" s="16" t="n"/>
+      <c r="K17" s="16" t="n"/>
+      <c r="L17" s="16" t="n"/>
+      <c r="M17" s="16" t="n"/>
+      <c r="N17" s="16" t="n"/>
+      <c r="O17" s="16" t="n"/>
+      <c r="P17" s="16" t="n"/>
+      <c r="Q17" s="17">
+        <f>SUM(Q6:Q16)</f>
+        <v/>
+      </c>
+      <c r="R17" s="16" t="n"/>
+      <c r="S17" s="16" t="n"/>
+      <c r="T17" s="18">
+        <f>SUM(T6:T16)</f>
+        <v/>
+      </c>
+      <c r="U17" s="18">
+        <f>SUM(U6:U16)</f>
+        <v/>
+      </c>
+      <c r="V17" s="18">
+        <f>SUM(V6:V16)</f>
+        <v/>
+      </c>
+      <c r="W17" s="16" t="n"/>
+      <c r="X17" s="18">
+        <f>SUM(X6:X16)</f>
+        <v/>
+      </c>
+      <c r="Y17" s="18">
+        <f>SUM(Y6:Y16)</f>
+        <v/>
+      </c>
+      <c r="Z17" s="19">
+        <f>SUM(Z6:Z16)</f>
+        <v/>
+      </c>
+      <c r="AA17" s="16" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:Z17"/>
-  <mergeCells count="5">
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="A3:Z3"/>
-    <mergeCell ref="A20:Z20"/>
-    <mergeCell ref="A2:Z2"/>
-    <mergeCell ref="A18:R18"/>
+  <autoFilter ref="A5:AA16"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="A17:P17"/>
+    <mergeCell ref="A3:AA3"/>
+    <mergeCell ref="A2:AA2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="D6:D17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D6:D16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Cliente,Interna"</formula1>
     </dataValidation>
-    <dataValidation sqref="E6:E17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"In presenza,Remoto,Interna,Da definire"</formula1>
+    <dataValidation sqref="E6:E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"In presenza,Remoto,Interna"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2446,9 +2361,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="5.5" customWidth="1" min="7" max="7"/>
@@ -2468,7 +2383,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>›  TIMELINE DI PROGETTO — SOVRAPPOSIZIONE DELLE FASI PER SETTIMANA</t>
+          <t>›  TIMELINE DI PROGETTO — 10 SETTIMANE + CODA DI TRADUZIONE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2489,10 +2404,10 @@
       <c r="Q1" s="2" t="n"/>
       <c r="R1" s="2" t="n"/>
     </row>
-    <row r="2" ht="24" customHeight="1">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Le barre si disegnano da sole dalle settimane impostate nella WBS: qui non si scrive nulla. GIALLO = le fasi che si svolgono nelle STESSE settimane, in parallelo. NERO = altra fase con il cliente. GRIGIO = fase interna. La riga in fondo conta quante fasi sono attive in ciascuna settimana.</t>
+          <t>Le barre si disegnano da sole dalle settimane impostate nella WBS: qui non si scrive nulla. GIALLO = i 5 workshop, il nucleo erogato dell'assessment. NERO = altra sessione con il cliente. GRIGIO = fase interna. La riga in fondo conta quante fasi sono attive in ciascuna settimana. Vincolo contrattuale: il meeting di presentazione cade circa 15 giorni dopo il Workshop #5.</t>
         </is>
       </c>
     </row>
@@ -2529,1085 +2444,1028 @@
 sett.</t>
         </is>
       </c>
-      <c r="G4" s="27" t="n">
+      <c r="G4" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="27" t="n">
+      <c r="H4" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I4" s="27" t="n">
+      <c r="I4" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="27" t="n">
+      <c r="J4" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="K4" s="27" t="n">
+      <c r="K4" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="27" t="n">
+      <c r="L4" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="M4" s="27" t="n">
+      <c r="M4" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="N4" s="27" t="n">
+      <c r="N4" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="O4" s="27" t="n">
+      <c r="O4" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="P4" s="27" t="n">
+      <c r="P4" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="Q4" s="27" t="n">
+      <c r="Q4" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="R4" s="27" t="n">
+      <c r="R4" s="20" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Settimane con fasi in parallelo  ›</t>
         </is>
       </c>
-      <c r="G5" s="29">
-        <f>IF(G18&gt;1,"›","")</f>
-        <v/>
-      </c>
-      <c r="H5" s="29">
-        <f>IF(H18&gt;1,"›","")</f>
-        <v/>
-      </c>
-      <c r="I5" s="29">
-        <f>IF(I18&gt;1,"›","")</f>
-        <v/>
-      </c>
-      <c r="J5" s="29">
-        <f>IF(J18&gt;1,"›","")</f>
-        <v/>
-      </c>
-      <c r="K5" s="29">
-        <f>IF(K18&gt;1,"›","")</f>
-        <v/>
-      </c>
-      <c r="L5" s="29">
-        <f>IF(L18&gt;1,"›","")</f>
-        <v/>
-      </c>
-      <c r="M5" s="29">
-        <f>IF(M18&gt;1,"›","")</f>
-        <v/>
-      </c>
-      <c r="N5" s="29">
-        <f>IF(N18&gt;1,"›","")</f>
-        <v/>
-      </c>
-      <c r="O5" s="29">
-        <f>IF(O18&gt;1,"›","")</f>
-        <v/>
-      </c>
-      <c r="P5" s="29">
-        <f>IF(P18&gt;1,"›","")</f>
-        <v/>
-      </c>
-      <c r="Q5" s="29">
-        <f>IF(Q18&gt;1,"›","")</f>
-        <v/>
-      </c>
-      <c r="R5" s="29">
-        <f>IF(R18&gt;1,"›","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="30">
+      <c r="B5" s="22" t="n"/>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="22" t="n"/>
+      <c r="F5" s="22" t="n"/>
+      <c r="G5" s="23">
+        <f>IF(G17&gt;1,"›","")</f>
+        <v/>
+      </c>
+      <c r="H5" s="23">
+        <f>IF(H17&gt;1,"›","")</f>
+        <v/>
+      </c>
+      <c r="I5" s="23">
+        <f>IF(I17&gt;1,"›","")</f>
+        <v/>
+      </c>
+      <c r="J5" s="23">
+        <f>IF(J17&gt;1,"›","")</f>
+        <v/>
+      </c>
+      <c r="K5" s="23">
+        <f>IF(K17&gt;1,"›","")</f>
+        <v/>
+      </c>
+      <c r="L5" s="23">
+        <f>IF(L17&gt;1,"›","")</f>
+        <v/>
+      </c>
+      <c r="M5" s="23">
+        <f>IF(M17&gt;1,"›","")</f>
+        <v/>
+      </c>
+      <c r="N5" s="23">
+        <f>IF(N17&gt;1,"›","")</f>
+        <v/>
+      </c>
+      <c r="O5" s="23">
+        <f>IF(O17&gt;1,"›","")</f>
+        <v/>
+      </c>
+      <c r="P5" s="23">
+        <f>IF(P17&gt;1,"›","")</f>
+        <v/>
+      </c>
+      <c r="Q5" s="23">
+        <f>IF(Q17&gt;1,"›","")</f>
+        <v/>
+      </c>
+      <c r="R5" s="23">
+        <f>IF(R17&gt;1,"›","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="24">
         <f>WBS!A6</f>
         <v/>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="25">
         <f>WBS!C6</f>
         <v/>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="26">
         <f>WBS!D6</f>
         <v/>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="27">
         <f>WBS!F6</f>
         <v/>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="24">
         <f>WBS!G6</f>
         <v/>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="24">
         <f>WBS!I6</f>
         <v/>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="28">
         <f>IF(AND($E6&lt;&gt;"",$F6&lt;&gt;"",$E6&lt;=G$4,$F6&gt;=G$4),1,"")</f>
         <v/>
       </c>
-      <c r="H6" s="34">
+      <c r="H6" s="28">
         <f>IF(AND($E6&lt;&gt;"",$F6&lt;&gt;"",$E6&lt;=H$4,$F6&gt;=H$4),1,"")</f>
         <v/>
       </c>
-      <c r="I6" s="34">
+      <c r="I6" s="28">
         <f>IF(AND($E6&lt;&gt;"",$F6&lt;&gt;"",$E6&lt;=I$4,$F6&gt;=I$4),1,"")</f>
         <v/>
       </c>
-      <c r="J6" s="34">
+      <c r="J6" s="28">
         <f>IF(AND($E6&lt;&gt;"",$F6&lt;&gt;"",$E6&lt;=J$4,$F6&gt;=J$4),1,"")</f>
         <v/>
       </c>
-      <c r="K6" s="34">
+      <c r="K6" s="28">
         <f>IF(AND($E6&lt;&gt;"",$F6&lt;&gt;"",$E6&lt;=K$4,$F6&gt;=K$4),1,"")</f>
         <v/>
       </c>
-      <c r="L6" s="34">
+      <c r="L6" s="28">
         <f>IF(AND($E6&lt;&gt;"",$F6&lt;&gt;"",$E6&lt;=L$4,$F6&gt;=L$4),1,"")</f>
         <v/>
       </c>
-      <c r="M6" s="34">
+      <c r="M6" s="28">
         <f>IF(AND($E6&lt;&gt;"",$F6&lt;&gt;"",$E6&lt;=M$4,$F6&gt;=M$4),1,"")</f>
         <v/>
       </c>
-      <c r="N6" s="34">
+      <c r="N6" s="28">
         <f>IF(AND($E6&lt;&gt;"",$F6&lt;&gt;"",$E6&lt;=N$4,$F6&gt;=N$4),1,"")</f>
         <v/>
       </c>
-      <c r="O6" s="34">
+      <c r="O6" s="28">
         <f>IF(AND($E6&lt;&gt;"",$F6&lt;&gt;"",$E6&lt;=O$4,$F6&gt;=O$4),1,"")</f>
         <v/>
       </c>
-      <c r="P6" s="34">
+      <c r="P6" s="28">
         <f>IF(AND($E6&lt;&gt;"",$F6&lt;&gt;"",$E6&lt;=P$4,$F6&gt;=P$4),1,"")</f>
         <v/>
       </c>
-      <c r="Q6" s="34">
+      <c r="Q6" s="28">
         <f>IF(AND($E6&lt;&gt;"",$F6&lt;&gt;"",$E6&lt;=Q$4,$F6&gt;=Q$4),1,"")</f>
         <v/>
       </c>
-      <c r="R6" s="34">
+      <c r="R6" s="28">
         <f>IF(AND($E6&lt;&gt;"",$F6&lt;&gt;"",$E6&lt;=R$4,$F6&gt;=R$4),1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="30">
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="24">
         <f>WBS!A7</f>
         <v/>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="25">
         <f>WBS!C7</f>
         <v/>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="26">
         <f>WBS!D7</f>
         <v/>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="27">
         <f>WBS!F7</f>
         <v/>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="24">
         <f>WBS!G7</f>
         <v/>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="24">
         <f>WBS!I7</f>
         <v/>
       </c>
-      <c r="G7" s="34">
+      <c r="G7" s="28">
         <f>IF(AND($E7&lt;&gt;"",$F7&lt;&gt;"",$E7&lt;=G$4,$F7&gt;=G$4),1,"")</f>
         <v/>
       </c>
-      <c r="H7" s="34">
+      <c r="H7" s="28">
         <f>IF(AND($E7&lt;&gt;"",$F7&lt;&gt;"",$E7&lt;=H$4,$F7&gt;=H$4),1,"")</f>
         <v/>
       </c>
-      <c r="I7" s="34">
+      <c r="I7" s="28">
         <f>IF(AND($E7&lt;&gt;"",$F7&lt;&gt;"",$E7&lt;=I$4,$F7&gt;=I$4),1,"")</f>
         <v/>
       </c>
-      <c r="J7" s="34">
+      <c r="J7" s="28">
         <f>IF(AND($E7&lt;&gt;"",$F7&lt;&gt;"",$E7&lt;=J$4,$F7&gt;=J$4),1,"")</f>
         <v/>
       </c>
-      <c r="K7" s="34">
+      <c r="K7" s="28">
         <f>IF(AND($E7&lt;&gt;"",$F7&lt;&gt;"",$E7&lt;=K$4,$F7&gt;=K$4),1,"")</f>
         <v/>
       </c>
-      <c r="L7" s="34">
+      <c r="L7" s="28">
         <f>IF(AND($E7&lt;&gt;"",$F7&lt;&gt;"",$E7&lt;=L$4,$F7&gt;=L$4),1,"")</f>
         <v/>
       </c>
-      <c r="M7" s="34">
+      <c r="M7" s="28">
         <f>IF(AND($E7&lt;&gt;"",$F7&lt;&gt;"",$E7&lt;=M$4,$F7&gt;=M$4),1,"")</f>
         <v/>
       </c>
-      <c r="N7" s="34">
+      <c r="N7" s="28">
         <f>IF(AND($E7&lt;&gt;"",$F7&lt;&gt;"",$E7&lt;=N$4,$F7&gt;=N$4),1,"")</f>
         <v/>
       </c>
-      <c r="O7" s="34">
+      <c r="O7" s="28">
         <f>IF(AND($E7&lt;&gt;"",$F7&lt;&gt;"",$E7&lt;=O$4,$F7&gt;=O$4),1,"")</f>
         <v/>
       </c>
-      <c r="P7" s="34">
+      <c r="P7" s="28">
         <f>IF(AND($E7&lt;&gt;"",$F7&lt;&gt;"",$E7&lt;=P$4,$F7&gt;=P$4),1,"")</f>
         <v/>
       </c>
-      <c r="Q7" s="34">
+      <c r="Q7" s="28">
         <f>IF(AND($E7&lt;&gt;"",$F7&lt;&gt;"",$E7&lt;=Q$4,$F7&gt;=Q$4),1,"")</f>
         <v/>
       </c>
-      <c r="R7" s="34">
+      <c r="R7" s="28">
         <f>IF(AND($E7&lt;&gt;"",$F7&lt;&gt;"",$E7&lt;=R$4,$F7&gt;=R$4),1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="30">
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="24">
         <f>WBS!A8</f>
         <v/>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="25">
         <f>WBS!C8</f>
         <v/>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="26">
         <f>WBS!D8</f>
         <v/>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="27">
         <f>WBS!F8</f>
         <v/>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="24">
         <f>WBS!G8</f>
         <v/>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="24">
         <f>WBS!I8</f>
         <v/>
       </c>
-      <c r="G8" s="34">
+      <c r="G8" s="28">
         <f>IF(AND($E8&lt;&gt;"",$F8&lt;&gt;"",$E8&lt;=G$4,$F8&gt;=G$4),1,"")</f>
         <v/>
       </c>
-      <c r="H8" s="34">
+      <c r="H8" s="28">
         <f>IF(AND($E8&lt;&gt;"",$F8&lt;&gt;"",$E8&lt;=H$4,$F8&gt;=H$4),1,"")</f>
         <v/>
       </c>
-      <c r="I8" s="34">
+      <c r="I8" s="28">
         <f>IF(AND($E8&lt;&gt;"",$F8&lt;&gt;"",$E8&lt;=I$4,$F8&gt;=I$4),1,"")</f>
         <v/>
       </c>
-      <c r="J8" s="34">
+      <c r="J8" s="28">
         <f>IF(AND($E8&lt;&gt;"",$F8&lt;&gt;"",$E8&lt;=J$4,$F8&gt;=J$4),1,"")</f>
         <v/>
       </c>
-      <c r="K8" s="34">
+      <c r="K8" s="28">
         <f>IF(AND($E8&lt;&gt;"",$F8&lt;&gt;"",$E8&lt;=K$4,$F8&gt;=K$4),1,"")</f>
         <v/>
       </c>
-      <c r="L8" s="34">
+      <c r="L8" s="28">
         <f>IF(AND($E8&lt;&gt;"",$F8&lt;&gt;"",$E8&lt;=L$4,$F8&gt;=L$4),1,"")</f>
         <v/>
       </c>
-      <c r="M8" s="34">
+      <c r="M8" s="28">
         <f>IF(AND($E8&lt;&gt;"",$F8&lt;&gt;"",$E8&lt;=M$4,$F8&gt;=M$4),1,"")</f>
         <v/>
       </c>
-      <c r="N8" s="34">
+      <c r="N8" s="28">
         <f>IF(AND($E8&lt;&gt;"",$F8&lt;&gt;"",$E8&lt;=N$4,$F8&gt;=N$4),1,"")</f>
         <v/>
       </c>
-      <c r="O8" s="34">
+      <c r="O8" s="28">
         <f>IF(AND($E8&lt;&gt;"",$F8&lt;&gt;"",$E8&lt;=O$4,$F8&gt;=O$4),1,"")</f>
         <v/>
       </c>
-      <c r="P8" s="34">
+      <c r="P8" s="28">
         <f>IF(AND($E8&lt;&gt;"",$F8&lt;&gt;"",$E8&lt;=P$4,$F8&gt;=P$4),1,"")</f>
         <v/>
       </c>
-      <c r="Q8" s="34">
+      <c r="Q8" s="28">
         <f>IF(AND($E8&lt;&gt;"",$F8&lt;&gt;"",$E8&lt;=Q$4,$F8&gt;=Q$4),1,"")</f>
         <v/>
       </c>
-      <c r="R8" s="34">
+      <c r="R8" s="28">
         <f>IF(AND($E8&lt;&gt;"",$F8&lt;&gt;"",$E8&lt;=R$4,$F8&gt;=R$4),1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="30">
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="24">
         <f>WBS!A9</f>
         <v/>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="25">
         <f>WBS!C9</f>
         <v/>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="26">
         <f>WBS!D9</f>
         <v/>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="27">
         <f>WBS!F9</f>
         <v/>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="24">
         <f>WBS!G9</f>
         <v/>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="24">
         <f>WBS!I9</f>
         <v/>
       </c>
-      <c r="G9" s="34">
+      <c r="G9" s="28">
         <f>IF(AND($E9&lt;&gt;"",$F9&lt;&gt;"",$E9&lt;=G$4,$F9&gt;=G$4),1,"")</f>
         <v/>
       </c>
-      <c r="H9" s="34">
+      <c r="H9" s="28">
         <f>IF(AND($E9&lt;&gt;"",$F9&lt;&gt;"",$E9&lt;=H$4,$F9&gt;=H$4),1,"")</f>
         <v/>
       </c>
-      <c r="I9" s="34">
+      <c r="I9" s="28">
         <f>IF(AND($E9&lt;&gt;"",$F9&lt;&gt;"",$E9&lt;=I$4,$F9&gt;=I$4),1,"")</f>
         <v/>
       </c>
-      <c r="J9" s="34">
+      <c r="J9" s="28">
         <f>IF(AND($E9&lt;&gt;"",$F9&lt;&gt;"",$E9&lt;=J$4,$F9&gt;=J$4),1,"")</f>
         <v/>
       </c>
-      <c r="K9" s="34">
+      <c r="K9" s="28">
         <f>IF(AND($E9&lt;&gt;"",$F9&lt;&gt;"",$E9&lt;=K$4,$F9&gt;=K$4),1,"")</f>
         <v/>
       </c>
-      <c r="L9" s="34">
+      <c r="L9" s="28">
         <f>IF(AND($E9&lt;&gt;"",$F9&lt;&gt;"",$E9&lt;=L$4,$F9&gt;=L$4),1,"")</f>
         <v/>
       </c>
-      <c r="M9" s="34">
+      <c r="M9" s="28">
         <f>IF(AND($E9&lt;&gt;"",$F9&lt;&gt;"",$E9&lt;=M$4,$F9&gt;=M$4),1,"")</f>
         <v/>
       </c>
-      <c r="N9" s="34">
+      <c r="N9" s="28">
         <f>IF(AND($E9&lt;&gt;"",$F9&lt;&gt;"",$E9&lt;=N$4,$F9&gt;=N$4),1,"")</f>
         <v/>
       </c>
-      <c r="O9" s="34">
+      <c r="O9" s="28">
         <f>IF(AND($E9&lt;&gt;"",$F9&lt;&gt;"",$E9&lt;=O$4,$F9&gt;=O$4),1,"")</f>
         <v/>
       </c>
-      <c r="P9" s="34">
+      <c r="P9" s="28">
         <f>IF(AND($E9&lt;&gt;"",$F9&lt;&gt;"",$E9&lt;=P$4,$F9&gt;=P$4),1,"")</f>
         <v/>
       </c>
-      <c r="Q9" s="34">
+      <c r="Q9" s="28">
         <f>IF(AND($E9&lt;&gt;"",$F9&lt;&gt;"",$E9&lt;=Q$4,$F9&gt;=Q$4),1,"")</f>
         <v/>
       </c>
-      <c r="R9" s="34">
+      <c r="R9" s="28">
         <f>IF(AND($E9&lt;&gt;"",$F9&lt;&gt;"",$E9&lt;=R$4,$F9&gt;=R$4),1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="30">
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="24">
         <f>WBS!A10</f>
         <v/>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="25">
         <f>WBS!C10</f>
         <v/>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="26">
         <f>WBS!D10</f>
         <v/>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="27">
         <f>WBS!F10</f>
         <v/>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="24">
         <f>WBS!G10</f>
         <v/>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="24">
         <f>WBS!I10</f>
         <v/>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="28">
         <f>IF(AND($E10&lt;&gt;"",$F10&lt;&gt;"",$E10&lt;=G$4,$F10&gt;=G$4),1,"")</f>
         <v/>
       </c>
-      <c r="H10" s="34">
+      <c r="H10" s="28">
         <f>IF(AND($E10&lt;&gt;"",$F10&lt;&gt;"",$E10&lt;=H$4,$F10&gt;=H$4),1,"")</f>
         <v/>
       </c>
-      <c r="I10" s="34">
+      <c r="I10" s="28">
         <f>IF(AND($E10&lt;&gt;"",$F10&lt;&gt;"",$E10&lt;=I$4,$F10&gt;=I$4),1,"")</f>
         <v/>
       </c>
-      <c r="J10" s="34">
+      <c r="J10" s="28">
         <f>IF(AND($E10&lt;&gt;"",$F10&lt;&gt;"",$E10&lt;=J$4,$F10&gt;=J$4),1,"")</f>
         <v/>
       </c>
-      <c r="K10" s="34">
+      <c r="K10" s="28">
         <f>IF(AND($E10&lt;&gt;"",$F10&lt;&gt;"",$E10&lt;=K$4,$F10&gt;=K$4),1,"")</f>
         <v/>
       </c>
-      <c r="L10" s="34">
+      <c r="L10" s="28">
         <f>IF(AND($E10&lt;&gt;"",$F10&lt;&gt;"",$E10&lt;=L$4,$F10&gt;=L$4),1,"")</f>
         <v/>
       </c>
-      <c r="M10" s="34">
+      <c r="M10" s="28">
         <f>IF(AND($E10&lt;&gt;"",$F10&lt;&gt;"",$E10&lt;=M$4,$F10&gt;=M$4),1,"")</f>
         <v/>
       </c>
-      <c r="N10" s="34">
+      <c r="N10" s="28">
         <f>IF(AND($E10&lt;&gt;"",$F10&lt;&gt;"",$E10&lt;=N$4,$F10&gt;=N$4),1,"")</f>
         <v/>
       </c>
-      <c r="O10" s="34">
+      <c r="O10" s="28">
         <f>IF(AND($E10&lt;&gt;"",$F10&lt;&gt;"",$E10&lt;=O$4,$F10&gt;=O$4),1,"")</f>
         <v/>
       </c>
-      <c r="P10" s="34">
+      <c r="P10" s="28">
         <f>IF(AND($E10&lt;&gt;"",$F10&lt;&gt;"",$E10&lt;=P$4,$F10&gt;=P$4),1,"")</f>
         <v/>
       </c>
-      <c r="Q10" s="34">
+      <c r="Q10" s="28">
         <f>IF(AND($E10&lt;&gt;"",$F10&lt;&gt;"",$E10&lt;=Q$4,$F10&gt;=Q$4),1,"")</f>
         <v/>
       </c>
-      <c r="R10" s="34">
+      <c r="R10" s="28">
         <f>IF(AND($E10&lt;&gt;"",$F10&lt;&gt;"",$E10&lt;=R$4,$F10&gt;=R$4),1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="30">
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="24">
         <f>WBS!A11</f>
         <v/>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="25">
         <f>WBS!C11</f>
         <v/>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="26">
         <f>WBS!D11</f>
         <v/>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="27">
         <f>WBS!F11</f>
         <v/>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="24">
         <f>WBS!G11</f>
         <v/>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="24">
         <f>WBS!I11</f>
         <v/>
       </c>
-      <c r="G11" s="34">
+      <c r="G11" s="28">
         <f>IF(AND($E11&lt;&gt;"",$F11&lt;&gt;"",$E11&lt;=G$4,$F11&gt;=G$4),1,"")</f>
         <v/>
       </c>
-      <c r="H11" s="34">
+      <c r="H11" s="28">
         <f>IF(AND($E11&lt;&gt;"",$F11&lt;&gt;"",$E11&lt;=H$4,$F11&gt;=H$4),1,"")</f>
         <v/>
       </c>
-      <c r="I11" s="34">
+      <c r="I11" s="28">
         <f>IF(AND($E11&lt;&gt;"",$F11&lt;&gt;"",$E11&lt;=I$4,$F11&gt;=I$4),1,"")</f>
         <v/>
       </c>
-      <c r="J11" s="34">
+      <c r="J11" s="28">
         <f>IF(AND($E11&lt;&gt;"",$F11&lt;&gt;"",$E11&lt;=J$4,$F11&gt;=J$4),1,"")</f>
         <v/>
       </c>
-      <c r="K11" s="34">
+      <c r="K11" s="28">
         <f>IF(AND($E11&lt;&gt;"",$F11&lt;&gt;"",$E11&lt;=K$4,$F11&gt;=K$4),1,"")</f>
         <v/>
       </c>
-      <c r="L11" s="34">
+      <c r="L11" s="28">
         <f>IF(AND($E11&lt;&gt;"",$F11&lt;&gt;"",$E11&lt;=L$4,$F11&gt;=L$4),1,"")</f>
         <v/>
       </c>
-      <c r="M11" s="34">
+      <c r="M11" s="28">
         <f>IF(AND($E11&lt;&gt;"",$F11&lt;&gt;"",$E11&lt;=M$4,$F11&gt;=M$4),1,"")</f>
         <v/>
       </c>
-      <c r="N11" s="34">
+      <c r="N11" s="28">
         <f>IF(AND($E11&lt;&gt;"",$F11&lt;&gt;"",$E11&lt;=N$4,$F11&gt;=N$4),1,"")</f>
         <v/>
       </c>
-      <c r="O11" s="34">
+      <c r="O11" s="28">
         <f>IF(AND($E11&lt;&gt;"",$F11&lt;&gt;"",$E11&lt;=O$4,$F11&gt;=O$4),1,"")</f>
         <v/>
       </c>
-      <c r="P11" s="34">
+      <c r="P11" s="28">
         <f>IF(AND($E11&lt;&gt;"",$F11&lt;&gt;"",$E11&lt;=P$4,$F11&gt;=P$4),1,"")</f>
         <v/>
       </c>
-      <c r="Q11" s="34">
+      <c r="Q11" s="28">
         <f>IF(AND($E11&lt;&gt;"",$F11&lt;&gt;"",$E11&lt;=Q$4,$F11&gt;=Q$4),1,"")</f>
         <v/>
       </c>
-      <c r="R11" s="34">
+      <c r="R11" s="28">
         <f>IF(AND($E11&lt;&gt;"",$F11&lt;&gt;"",$E11&lt;=R$4,$F11&gt;=R$4),1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="30">
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="24">
         <f>WBS!A12</f>
         <v/>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="25">
         <f>WBS!C12</f>
         <v/>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="26">
         <f>WBS!D12</f>
         <v/>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="27">
         <f>WBS!F12</f>
         <v/>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="24">
         <f>WBS!G12</f>
         <v/>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="24">
         <f>WBS!I12</f>
         <v/>
       </c>
-      <c r="G12" s="34">
+      <c r="G12" s="28">
         <f>IF(AND($E12&lt;&gt;"",$F12&lt;&gt;"",$E12&lt;=G$4,$F12&gt;=G$4),1,"")</f>
         <v/>
       </c>
-      <c r="H12" s="34">
+      <c r="H12" s="28">
         <f>IF(AND($E12&lt;&gt;"",$F12&lt;&gt;"",$E12&lt;=H$4,$F12&gt;=H$4),1,"")</f>
         <v/>
       </c>
-      <c r="I12" s="34">
+      <c r="I12" s="28">
         <f>IF(AND($E12&lt;&gt;"",$F12&lt;&gt;"",$E12&lt;=I$4,$F12&gt;=I$4),1,"")</f>
         <v/>
       </c>
-      <c r="J12" s="34">
+      <c r="J12" s="28">
         <f>IF(AND($E12&lt;&gt;"",$F12&lt;&gt;"",$E12&lt;=J$4,$F12&gt;=J$4),1,"")</f>
         <v/>
       </c>
-      <c r="K12" s="34">
+      <c r="K12" s="28">
         <f>IF(AND($E12&lt;&gt;"",$F12&lt;&gt;"",$E12&lt;=K$4,$F12&gt;=K$4),1,"")</f>
         <v/>
       </c>
-      <c r="L12" s="34">
+      <c r="L12" s="28">
         <f>IF(AND($E12&lt;&gt;"",$F12&lt;&gt;"",$E12&lt;=L$4,$F12&gt;=L$4),1,"")</f>
         <v/>
       </c>
-      <c r="M12" s="34">
+      <c r="M12" s="28">
         <f>IF(AND($E12&lt;&gt;"",$F12&lt;&gt;"",$E12&lt;=M$4,$F12&gt;=M$4),1,"")</f>
         <v/>
       </c>
-      <c r="N12" s="34">
+      <c r="N12" s="28">
         <f>IF(AND($E12&lt;&gt;"",$F12&lt;&gt;"",$E12&lt;=N$4,$F12&gt;=N$4),1,"")</f>
         <v/>
       </c>
-      <c r="O12" s="34">
+      <c r="O12" s="28">
         <f>IF(AND($E12&lt;&gt;"",$F12&lt;&gt;"",$E12&lt;=O$4,$F12&gt;=O$4),1,"")</f>
         <v/>
       </c>
-      <c r="P12" s="34">
+      <c r="P12" s="28">
         <f>IF(AND($E12&lt;&gt;"",$F12&lt;&gt;"",$E12&lt;=P$4,$F12&gt;=P$4),1,"")</f>
         <v/>
       </c>
-      <c r="Q12" s="34">
+      <c r="Q12" s="28">
         <f>IF(AND($E12&lt;&gt;"",$F12&lt;&gt;"",$E12&lt;=Q$4,$F12&gt;=Q$4),1,"")</f>
         <v/>
       </c>
-      <c r="R12" s="34">
+      <c r="R12" s="28">
         <f>IF(AND($E12&lt;&gt;"",$F12&lt;&gt;"",$E12&lt;=R$4,$F12&gt;=R$4),1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="30">
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="24">
         <f>WBS!A13</f>
         <v/>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="25">
         <f>WBS!C13</f>
         <v/>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="26">
         <f>WBS!D13</f>
         <v/>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="27">
         <f>WBS!F13</f>
         <v/>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="24">
         <f>WBS!G13</f>
         <v/>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="24">
         <f>WBS!I13</f>
         <v/>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="28">
         <f>IF(AND($E13&lt;&gt;"",$F13&lt;&gt;"",$E13&lt;=G$4,$F13&gt;=G$4),1,"")</f>
         <v/>
       </c>
-      <c r="H13" s="34">
+      <c r="H13" s="28">
         <f>IF(AND($E13&lt;&gt;"",$F13&lt;&gt;"",$E13&lt;=H$4,$F13&gt;=H$4),1,"")</f>
         <v/>
       </c>
-      <c r="I13" s="34">
+      <c r="I13" s="28">
         <f>IF(AND($E13&lt;&gt;"",$F13&lt;&gt;"",$E13&lt;=I$4,$F13&gt;=I$4),1,"")</f>
         <v/>
       </c>
-      <c r="J13" s="34">
+      <c r="J13" s="28">
         <f>IF(AND($E13&lt;&gt;"",$F13&lt;&gt;"",$E13&lt;=J$4,$F13&gt;=J$4),1,"")</f>
         <v/>
       </c>
-      <c r="K13" s="34">
+      <c r="K13" s="28">
         <f>IF(AND($E13&lt;&gt;"",$F13&lt;&gt;"",$E13&lt;=K$4,$F13&gt;=K$4),1,"")</f>
         <v/>
       </c>
-      <c r="L13" s="34">
+      <c r="L13" s="28">
         <f>IF(AND($E13&lt;&gt;"",$F13&lt;&gt;"",$E13&lt;=L$4,$F13&gt;=L$4),1,"")</f>
         <v/>
       </c>
-      <c r="M13" s="34">
+      <c r="M13" s="28">
         <f>IF(AND($E13&lt;&gt;"",$F13&lt;&gt;"",$E13&lt;=M$4,$F13&gt;=M$4),1,"")</f>
         <v/>
       </c>
-      <c r="N13" s="34">
+      <c r="N13" s="28">
         <f>IF(AND($E13&lt;&gt;"",$F13&lt;&gt;"",$E13&lt;=N$4,$F13&gt;=N$4),1,"")</f>
         <v/>
       </c>
-      <c r="O13" s="34">
+      <c r="O13" s="28">
         <f>IF(AND($E13&lt;&gt;"",$F13&lt;&gt;"",$E13&lt;=O$4,$F13&gt;=O$4),1,"")</f>
         <v/>
       </c>
-      <c r="P13" s="34">
+      <c r="P13" s="28">
         <f>IF(AND($E13&lt;&gt;"",$F13&lt;&gt;"",$E13&lt;=P$4,$F13&gt;=P$4),1,"")</f>
         <v/>
       </c>
-      <c r="Q13" s="34">
+      <c r="Q13" s="28">
         <f>IF(AND($E13&lt;&gt;"",$F13&lt;&gt;"",$E13&lt;=Q$4,$F13&gt;=Q$4),1,"")</f>
         <v/>
       </c>
-      <c r="R13" s="34">
+      <c r="R13" s="28">
         <f>IF(AND($E13&lt;&gt;"",$F13&lt;&gt;"",$E13&lt;=R$4,$F13&gt;=R$4),1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="30">
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="24">
         <f>WBS!A14</f>
         <v/>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="25">
         <f>WBS!C14</f>
         <v/>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="26">
         <f>WBS!D14</f>
         <v/>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="27">
         <f>WBS!F14</f>
         <v/>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="24">
         <f>WBS!G14</f>
         <v/>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="24">
         <f>WBS!I14</f>
         <v/>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="28">
         <f>IF(AND($E14&lt;&gt;"",$F14&lt;&gt;"",$E14&lt;=G$4,$F14&gt;=G$4),1,"")</f>
         <v/>
       </c>
-      <c r="H14" s="34">
+      <c r="H14" s="28">
         <f>IF(AND($E14&lt;&gt;"",$F14&lt;&gt;"",$E14&lt;=H$4,$F14&gt;=H$4),1,"")</f>
         <v/>
       </c>
-      <c r="I14" s="34">
+      <c r="I14" s="28">
         <f>IF(AND($E14&lt;&gt;"",$F14&lt;&gt;"",$E14&lt;=I$4,$F14&gt;=I$4),1,"")</f>
         <v/>
       </c>
-      <c r="J14" s="34">
+      <c r="J14" s="28">
         <f>IF(AND($E14&lt;&gt;"",$F14&lt;&gt;"",$E14&lt;=J$4,$F14&gt;=J$4),1,"")</f>
         <v/>
       </c>
-      <c r="K14" s="34">
+      <c r="K14" s="28">
         <f>IF(AND($E14&lt;&gt;"",$F14&lt;&gt;"",$E14&lt;=K$4,$F14&gt;=K$4),1,"")</f>
         <v/>
       </c>
-      <c r="L14" s="34">
+      <c r="L14" s="28">
         <f>IF(AND($E14&lt;&gt;"",$F14&lt;&gt;"",$E14&lt;=L$4,$F14&gt;=L$4),1,"")</f>
         <v/>
       </c>
-      <c r="M14" s="34">
+      <c r="M14" s="28">
         <f>IF(AND($E14&lt;&gt;"",$F14&lt;&gt;"",$E14&lt;=M$4,$F14&gt;=M$4),1,"")</f>
         <v/>
       </c>
-      <c r="N14" s="34">
+      <c r="N14" s="28">
         <f>IF(AND($E14&lt;&gt;"",$F14&lt;&gt;"",$E14&lt;=N$4,$F14&gt;=N$4),1,"")</f>
         <v/>
       </c>
-      <c r="O14" s="34">
+      <c r="O14" s="28">
         <f>IF(AND($E14&lt;&gt;"",$F14&lt;&gt;"",$E14&lt;=O$4,$F14&gt;=O$4),1,"")</f>
         <v/>
       </c>
-      <c r="P14" s="34">
+      <c r="P14" s="28">
         <f>IF(AND($E14&lt;&gt;"",$F14&lt;&gt;"",$E14&lt;=P$4,$F14&gt;=P$4),1,"")</f>
         <v/>
       </c>
-      <c r="Q14" s="34">
+      <c r="Q14" s="28">
         <f>IF(AND($E14&lt;&gt;"",$F14&lt;&gt;"",$E14&lt;=Q$4,$F14&gt;=Q$4),1,"")</f>
         <v/>
       </c>
-      <c r="R14" s="34">
+      <c r="R14" s="28">
         <f>IF(AND($E14&lt;&gt;"",$F14&lt;&gt;"",$E14&lt;=R$4,$F14&gt;=R$4),1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="30">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="24">
         <f>WBS!A15</f>
         <v/>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="25">
         <f>WBS!C15</f>
         <v/>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="26">
         <f>WBS!D15</f>
         <v/>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="27">
         <f>WBS!F15</f>
         <v/>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="24">
         <f>WBS!G15</f>
         <v/>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="24">
         <f>WBS!I15</f>
         <v/>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="28">
         <f>IF(AND($E15&lt;&gt;"",$F15&lt;&gt;"",$E15&lt;=G$4,$F15&gt;=G$4),1,"")</f>
         <v/>
       </c>
-      <c r="H15" s="34">
+      <c r="H15" s="28">
         <f>IF(AND($E15&lt;&gt;"",$F15&lt;&gt;"",$E15&lt;=H$4,$F15&gt;=H$4),1,"")</f>
         <v/>
       </c>
-      <c r="I15" s="34">
+      <c r="I15" s="28">
         <f>IF(AND($E15&lt;&gt;"",$F15&lt;&gt;"",$E15&lt;=I$4,$F15&gt;=I$4),1,"")</f>
         <v/>
       </c>
-      <c r="J15" s="34">
+      <c r="J15" s="28">
         <f>IF(AND($E15&lt;&gt;"",$F15&lt;&gt;"",$E15&lt;=J$4,$F15&gt;=J$4),1,"")</f>
         <v/>
       </c>
-      <c r="K15" s="34">
+      <c r="K15" s="28">
         <f>IF(AND($E15&lt;&gt;"",$F15&lt;&gt;"",$E15&lt;=K$4,$F15&gt;=K$4),1,"")</f>
         <v/>
       </c>
-      <c r="L15" s="34">
+      <c r="L15" s="28">
         <f>IF(AND($E15&lt;&gt;"",$F15&lt;&gt;"",$E15&lt;=L$4,$F15&gt;=L$4),1,"")</f>
         <v/>
       </c>
-      <c r="M15" s="34">
+      <c r="M15" s="28">
         <f>IF(AND($E15&lt;&gt;"",$F15&lt;&gt;"",$E15&lt;=M$4,$F15&gt;=M$4),1,"")</f>
         <v/>
       </c>
-      <c r="N15" s="34">
+      <c r="N15" s="28">
         <f>IF(AND($E15&lt;&gt;"",$F15&lt;&gt;"",$E15&lt;=N$4,$F15&gt;=N$4),1,"")</f>
         <v/>
       </c>
-      <c r="O15" s="34">
+      <c r="O15" s="28">
         <f>IF(AND($E15&lt;&gt;"",$F15&lt;&gt;"",$E15&lt;=O$4,$F15&gt;=O$4),1,"")</f>
         <v/>
       </c>
-      <c r="P15" s="34">
+      <c r="P15" s="28">
         <f>IF(AND($E15&lt;&gt;"",$F15&lt;&gt;"",$E15&lt;=P$4,$F15&gt;=P$4),1,"")</f>
         <v/>
       </c>
-      <c r="Q15" s="34">
+      <c r="Q15" s="28">
         <f>IF(AND($E15&lt;&gt;"",$F15&lt;&gt;"",$E15&lt;=Q$4,$F15&gt;=Q$4),1,"")</f>
         <v/>
       </c>
-      <c r="R15" s="34">
+      <c r="R15" s="28">
         <f>IF(AND($E15&lt;&gt;"",$F15&lt;&gt;"",$E15&lt;=R$4,$F15&gt;=R$4),1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="30">
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="24">
         <f>WBS!A16</f>
         <v/>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="25">
         <f>WBS!C16</f>
         <v/>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="26">
         <f>WBS!D16</f>
         <v/>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="27">
         <f>WBS!F16</f>
         <v/>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="24">
         <f>WBS!G16</f>
         <v/>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="24">
         <f>WBS!I16</f>
         <v/>
       </c>
-      <c r="G16" s="34">
+      <c r="G16" s="28">
         <f>IF(AND($E16&lt;&gt;"",$F16&lt;&gt;"",$E16&lt;=G$4,$F16&gt;=G$4),1,"")</f>
         <v/>
       </c>
-      <c r="H16" s="34">
+      <c r="H16" s="28">
         <f>IF(AND($E16&lt;&gt;"",$F16&lt;&gt;"",$E16&lt;=H$4,$F16&gt;=H$4),1,"")</f>
         <v/>
       </c>
-      <c r="I16" s="34">
+      <c r="I16" s="28">
         <f>IF(AND($E16&lt;&gt;"",$F16&lt;&gt;"",$E16&lt;=I$4,$F16&gt;=I$4),1,"")</f>
         <v/>
       </c>
-      <c r="J16" s="34">
+      <c r="J16" s="28">
         <f>IF(AND($E16&lt;&gt;"",$F16&lt;&gt;"",$E16&lt;=J$4,$F16&gt;=J$4),1,"")</f>
         <v/>
       </c>
-      <c r="K16" s="34">
+      <c r="K16" s="28">
         <f>IF(AND($E16&lt;&gt;"",$F16&lt;&gt;"",$E16&lt;=K$4,$F16&gt;=K$4),1,"")</f>
         <v/>
       </c>
-      <c r="L16" s="34">
+      <c r="L16" s="28">
         <f>IF(AND($E16&lt;&gt;"",$F16&lt;&gt;"",$E16&lt;=L$4,$F16&gt;=L$4),1,"")</f>
         <v/>
       </c>
-      <c r="M16" s="34">
+      <c r="M16" s="28">
         <f>IF(AND($E16&lt;&gt;"",$F16&lt;&gt;"",$E16&lt;=M$4,$F16&gt;=M$4),1,"")</f>
         <v/>
       </c>
-      <c r="N16" s="34">
+      <c r="N16" s="28">
         <f>IF(AND($E16&lt;&gt;"",$F16&lt;&gt;"",$E16&lt;=N$4,$F16&gt;=N$4),1,"")</f>
         <v/>
       </c>
-      <c r="O16" s="34">
+      <c r="O16" s="28">
         <f>IF(AND($E16&lt;&gt;"",$F16&lt;&gt;"",$E16&lt;=O$4,$F16&gt;=O$4),1,"")</f>
         <v/>
       </c>
-      <c r="P16" s="34">
+      <c r="P16" s="28">
         <f>IF(AND($E16&lt;&gt;"",$F16&lt;&gt;"",$E16&lt;=P$4,$F16&gt;=P$4),1,"")</f>
         <v/>
       </c>
-      <c r="Q16" s="34">
+      <c r="Q16" s="28">
         <f>IF(AND($E16&lt;&gt;"",$F16&lt;&gt;"",$E16&lt;=Q$4,$F16&gt;=Q$4),1,"")</f>
         <v/>
       </c>
-      <c r="R16" s="34">
+      <c r="R16" s="28">
         <f>IF(AND($E16&lt;&gt;"",$F16&lt;&gt;"",$E16&lt;=R$4,$F16&gt;=R$4),1,"")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="30">
-        <f>WBS!A17</f>
-        <v/>
-      </c>
-      <c r="B17" s="31">
-        <f>WBS!C17</f>
-        <v/>
-      </c>
-      <c r="C17" s="32">
-        <f>WBS!D17</f>
-        <v/>
-      </c>
-      <c r="D17" s="33">
-        <f>WBS!F17</f>
-        <v/>
-      </c>
-      <c r="E17" s="30">
-        <f>WBS!G17</f>
-        <v/>
-      </c>
-      <c r="F17" s="30">
-        <f>WBS!I17</f>
-        <v/>
-      </c>
-      <c r="G17" s="34">
-        <f>IF(AND($E17&lt;&gt;"",$F17&lt;&gt;"",$E17&lt;=G$4,$F17&gt;=G$4),1,"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="34">
-        <f>IF(AND($E17&lt;&gt;"",$F17&lt;&gt;"",$E17&lt;=H$4,$F17&gt;=H$4),1,"")</f>
-        <v/>
-      </c>
-      <c r="I17" s="34">
-        <f>IF(AND($E17&lt;&gt;"",$F17&lt;&gt;"",$E17&lt;=I$4,$F17&gt;=I$4),1,"")</f>
-        <v/>
-      </c>
-      <c r="J17" s="34">
-        <f>IF(AND($E17&lt;&gt;"",$F17&lt;&gt;"",$E17&lt;=J$4,$F17&gt;=J$4),1,"")</f>
-        <v/>
-      </c>
-      <c r="K17" s="34">
-        <f>IF(AND($E17&lt;&gt;"",$F17&lt;&gt;"",$E17&lt;=K$4,$F17&gt;=K$4),1,"")</f>
-        <v/>
-      </c>
-      <c r="L17" s="34">
-        <f>IF(AND($E17&lt;&gt;"",$F17&lt;&gt;"",$E17&lt;=L$4,$F17&gt;=L$4),1,"")</f>
-        <v/>
-      </c>
-      <c r="M17" s="34">
-        <f>IF(AND($E17&lt;&gt;"",$F17&lt;&gt;"",$E17&lt;=M$4,$F17&gt;=M$4),1,"")</f>
-        <v/>
-      </c>
-      <c r="N17" s="34">
-        <f>IF(AND($E17&lt;&gt;"",$F17&lt;&gt;"",$E17&lt;=N$4,$F17&gt;=N$4),1,"")</f>
-        <v/>
-      </c>
-      <c r="O17" s="34">
-        <f>IF(AND($E17&lt;&gt;"",$F17&lt;&gt;"",$E17&lt;=O$4,$F17&gt;=O$4),1,"")</f>
-        <v/>
-      </c>
-      <c r="P17" s="34">
-        <f>IF(AND($E17&lt;&gt;"",$F17&lt;&gt;"",$E17&lt;=P$4,$F17&gt;=P$4),1,"")</f>
-        <v/>
-      </c>
-      <c r="Q17" s="34">
-        <f>IF(AND($E17&lt;&gt;"",$F17&lt;&gt;"",$E17&lt;=Q$4,$F17&gt;=Q$4),1,"")</f>
-        <v/>
-      </c>
-      <c r="R17" s="34">
-        <f>IF(AND($E17&lt;&gt;"",$F17&lt;&gt;"",$E17&lt;=R$4,$F17&gt;=R$4),1,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="35" t="inlineStr">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>Fasi attive nella settimana</t>
         </is>
       </c>
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
-      <c r="G18" s="17">
-        <f>COUNT(G6:G17)</f>
-        <v/>
-      </c>
-      <c r="H18" s="17">
-        <f>COUNT(H6:H17)</f>
-        <v/>
-      </c>
-      <c r="I18" s="17">
-        <f>COUNT(I6:I17)</f>
-        <v/>
-      </c>
-      <c r="J18" s="17">
-        <f>COUNT(J6:J17)</f>
-        <v/>
-      </c>
-      <c r="K18" s="17">
-        <f>COUNT(K6:K17)</f>
-        <v/>
-      </c>
-      <c r="L18" s="17">
-        <f>COUNT(L6:L17)</f>
-        <v/>
-      </c>
-      <c r="M18" s="17">
-        <f>COUNT(M6:M17)</f>
-        <v/>
-      </c>
-      <c r="N18" s="17">
-        <f>COUNT(N6:N17)</f>
-        <v/>
-      </c>
-      <c r="O18" s="17">
-        <f>COUNT(O6:O17)</f>
-        <v/>
-      </c>
-      <c r="P18" s="17">
-        <f>COUNT(P6:P17)</f>
-        <v/>
-      </c>
-      <c r="Q18" s="17">
-        <f>COUNT(Q6:Q17)</f>
-        <v/>
-      </c>
-      <c r="R18" s="17">
-        <f>COUNT(R6:R17)</f>
+      <c r="B17" s="30" t="n"/>
+      <c r="C17" s="30" t="n"/>
+      <c r="D17" s="30" t="n"/>
+      <c r="E17" s="30" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="17">
+        <f>COUNT(G6:G16)</f>
+        <v/>
+      </c>
+      <c r="H17" s="17">
+        <f>COUNT(H6:H16)</f>
+        <v/>
+      </c>
+      <c r="I17" s="17">
+        <f>COUNT(I6:I16)</f>
+        <v/>
+      </c>
+      <c r="J17" s="17">
+        <f>COUNT(J6:J16)</f>
+        <v/>
+      </c>
+      <c r="K17" s="17">
+        <f>COUNT(K6:K16)</f>
+        <v/>
+      </c>
+      <c r="L17" s="17">
+        <f>COUNT(L6:L16)</f>
+        <v/>
+      </c>
+      <c r="M17" s="17">
+        <f>COUNT(M6:M16)</f>
+        <v/>
+      </c>
+      <c r="N17" s="17">
+        <f>COUNT(N6:N16)</f>
+        <v/>
+      </c>
+      <c r="O17" s="17">
+        <f>COUNT(O6:O16)</f>
+        <v/>
+      </c>
+      <c r="P17" s="17">
+        <f>COUNT(P6:P16)</f>
+        <v/>
+      </c>
+      <c r="Q17" s="17">
+        <f>COUNT(Q6:Q16)</f>
+        <v/>
+      </c>
+      <c r="R17" s="17">
+        <f>COUNT(R6:R16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>Sessioni erogate al cliente (n. incontri)</t>
+        </is>
+      </c>
+      <c r="F19" s="32">
+        <f>WBS!Q17</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="37" t="inlineStr">
-        <is>
-          <t>Settimane con più di una fase attiva in parallelo</t>
-        </is>
-      </c>
-      <c r="F20" s="38">
-        <f>COUNTIF(G18:R18,"&gt;1")</f>
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>di cui in presenza — trasferte incluse nell'investimento</t>
+        </is>
+      </c>
+      <c r="F20" s="32">
+        <f>SUMPRODUCT((WBS!$E$6:$E$16="In presenza")*WBS!$Q$6:$Q$16)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="37" t="inlineStr">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>Settimana di massima concentrazione (n. fasi in parallelo)</t>
         </is>
       </c>
-      <c r="F21" s="38">
-        <f>MAX(G18:R18)</f>
+      <c r="F21" s="32">
+        <f>MAX(G17:R17)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:R5">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>G5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6:R17">
+  <conditionalFormatting sqref="G6:R16">
     <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
-      <formula>AND(ISNUMBER(SEARCH("parallelo",$D6)),G6=1)</formula>
+      <formula>AND(ISNUMBER(SEARCH("Workshop",$D6)),G6=1)</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
       <formula>AND($C6="Interna",G6=1)</formula>
@@ -3616,14 +3474,14 @@
       <formula>G6=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B6:F17">
+  <conditionalFormatting sqref="B6:F16">
     <cfRule type="expression" priority="5" dxfId="4">
-      <formula>ISNUMBER(SEARCH("parallelo",$D6))</formula>
+      <formula>ISNUMBER(SEARCH("Workshop",$D6))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G18:R18">
+  <conditionalFormatting sqref="G17:R17">
     <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="1">
-      <formula>G18&gt;1</formula>
+      <formula>G17&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3637,14 +3495,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="2" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="64" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -3659,16 +3517,16 @@
       <c r="E1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="33" t="inlineStr">
         <is>
           <t>Tutti i valori sono calcolati dalla WBS e dai Parametri. Nessuna cella di questo foglio va compilata a mano.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="40" t="inlineStr">
-        <is>
-          <t>›  IMPEGNO E COSTO COMPLESSIVO</t>
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>›  IMPEGNO COMPLESSIVO</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -3679,19 +3537,23 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Giornate front office (presso il cliente)</t>
+          <t>Giornate front office (tempo erogato al cliente)</t>
         </is>
       </c>
       <c r="C5" s="14">
-        <f>WBS!S18</f>
-        <v/>
-      </c>
-      <c r="D5" s="41" t="inlineStr">
+        <f>WBS!T17</f>
+        <v/>
+      </c>
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>gg-uomo</t>
         </is>
       </c>
-      <c r="E5" s="42" t="inlineStr"/>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>Calcolate da n. incontri × durata × n. persone. Incontri in remoto inclusi.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -3700,15 +3562,19 @@
         </is>
       </c>
       <c r="C6" s="14">
-        <f>WBS!T18</f>
-        <v/>
-      </c>
-      <c r="D6" s="41" t="inlineStr">
+        <f>WBS!U17</f>
+        <v/>
+      </c>
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>gg-uomo</t>
         </is>
       </c>
-      <c r="E6" s="42" t="inlineStr"/>
+      <c r="E6" s="36" t="inlineStr">
+        <is>
+          <t>STIME Impresoft: il contratto non quantifica il back office.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -3717,17 +3583,17 @@
         </is>
       </c>
       <c r="C7" s="14">
-        <f>WBS!U18</f>
-        <v/>
-      </c>
-      <c r="D7" s="41" t="inlineStr">
+        <f>WBS!V17</f>
+        <v/>
+      </c>
+      <c r="D7" s="35" t="inlineStr">
         <is>
           <t>gg-uomo</t>
         </is>
       </c>
-      <c r="E7" s="42" t="inlineStr">
-        <is>
-          <t>Incluse nel monte ore, come da impostazione concordata.</t>
+      <c r="E7" s="36" t="inlineStr">
+        <is>
+          <t>Solo fasi in presenza. Incluse nel monte ore.</t>
         </is>
       </c>
     </row>
@@ -3737,16 +3603,16 @@
           <t>TOTALE giornate-uomo di progetto</t>
         </is>
       </c>
-      <c r="C8" s="43">
-        <f>WBS!W18</f>
-        <v/>
-      </c>
-      <c r="D8" s="41" t="inlineStr">
+      <c r="C8" s="37">
+        <f>WBS!X17</f>
+        <v/>
+      </c>
+      <c r="D8" s="35" t="inlineStr">
         <is>
           <t>gg-uomo</t>
         </is>
       </c>
-      <c r="E8" s="42" t="inlineStr"/>
+      <c r="E8" s="36" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -3754,125 +3620,125 @@
           <t>TOTALE ore di progetto</t>
         </is>
       </c>
-      <c r="C9" s="43">
-        <f>WBS!X18</f>
-        <v/>
-      </c>
-      <c r="D9" s="41" t="inlineStr">
+      <c r="C9" s="37">
+        <f>WBS!Y17</f>
+        <v/>
+      </c>
+      <c r="D9" s="35" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="E9" s="42" t="inlineStr">
-        <is>
-          <t>Totale giornate × ore per giornata (Parametri!$C$5).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>COSTO TOTALE DI PROGETTO</t>
-        </is>
-      </c>
-      <c r="C10" s="44">
-        <f>WBS!Y18</f>
-        <v/>
-      </c>
-      <c r="D10" s="41" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
+        <is>
+          <t>Totale giornate × ore per giornata (Parametri!$C$6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="34" t="inlineStr">
+        <is>
+          <t>›  COSTO DELLE GIORNATE</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Costo ore front office</t>
+        </is>
+      </c>
+      <c r="C12" s="15">
+        <f>WBS!T17*Parametri!$C$6*Parametri!$C$7</f>
+        <v/>
+      </c>
+      <c r="D12" s="35" t="inlineStr">
         <is>
           <t>€</t>
         </is>
       </c>
-      <c r="E10" s="42" t="inlineStr"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="40" t="inlineStr">
-        <is>
-          <t>›  RIPARTIZIONE DEL COSTO PER TIPOLOGIA DI ORA</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
+      <c r="E12" s="36" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>Costo ore front office</t>
+          <t>Costo ore back office</t>
         </is>
       </c>
       <c r="C13" s="15">
-        <f>WBS!S18*Parametri!$C$5*Parametri!$C$6</f>
-        <v/>
-      </c>
-      <c r="D13" s="41" t="inlineStr">
+        <f>WBS!U17*Parametri!$C$6*Parametri!$C$8</f>
+        <v/>
+      </c>
+      <c r="D13" s="35" t="inlineStr">
         <is>
           <t>€</t>
         </is>
       </c>
-      <c r="E13" s="42" t="inlineStr"/>
+      <c r="E13" s="36" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Costo ore back office</t>
+          <t>Costo ore di viaggio</t>
         </is>
       </c>
       <c r="C14" s="15">
-        <f>WBS!T18*Parametri!$C$5*Parametri!$C$7</f>
-        <v/>
-      </c>
-      <c r="D14" s="41" t="inlineStr">
+        <f>WBS!V17*Parametri!$C$6*Parametri!$C$9</f>
+        <v/>
+      </c>
+      <c r="D14" s="35" t="inlineStr">
         <is>
           <t>€</t>
         </is>
       </c>
-      <c r="E14" s="42" t="inlineStr"/>
+      <c r="E14" s="36" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Costo ore di viaggio</t>
-        </is>
-      </c>
-      <c r="C15" s="15">
-        <f>WBS!U18*Parametri!$C$5*Parametri!$C$8</f>
-        <v/>
-      </c>
-      <c r="D15" s="41" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>COSTO TOTALE DELLE GIORNATE</t>
+        </is>
+      </c>
+      <c r="C15" s="38">
+        <f>WBS!Z17</f>
+        <v/>
+      </c>
+      <c r="D15" s="35" t="inlineStr">
         <is>
           <t>€</t>
         </is>
       </c>
-      <c r="E15" s="42" t="inlineStr"/>
+      <c r="E15" s="36" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>Quadratura (deve coincidere con il costo totale)</t>
-        </is>
-      </c>
-      <c r="C16" s="44">
-        <f>SUM(C13:C15)</f>
-        <v/>
-      </c>
-      <c r="D16" s="41" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Quadratura (deve coincidere con la riga sopra)</t>
+        </is>
+      </c>
+      <c r="C16" s="15">
+        <f>SUM(C12:C14)</f>
+        <v/>
+      </c>
+      <c r="D16" s="35" t="inlineStr">
         <is>
           <t>€</t>
         </is>
       </c>
-      <c r="E16" s="42" t="inlineStr">
-        <is>
-          <t>Controllo interno: se differisce dal costo totale c'è un errore di formula.</t>
+      <c r="E16" s="36" t="inlineStr">
+        <is>
+          <t>Controllo interno: se differisce c'è un errore di formula.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="40" t="inlineStr">
-        <is>
-          <t>›  RIPARTIZIONE PER TIPO DI FASE</t>
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t>›  COSTO DELLE TRASFERTE — già incluso nell'investimento (Offerta § 10.1)</t>
         </is>
       </c>
       <c r="B18" s="5" t="n"/>
@@ -3883,349 +3749,697 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Giornate — fasi con il cliente</t>
-        </is>
-      </c>
-      <c r="C19" s="14">
-        <f>SUMIF(WBS!$D$6:$D$17,"Cliente",WBS!$W$6:$W$17)</f>
-        <v/>
-      </c>
-      <c r="D19" s="41" t="inlineStr">
-        <is>
-          <t>gg-uomo</t>
-        </is>
-      </c>
-      <c r="E19" s="42" t="inlineStr"/>
+          <t>Sessioni in presenza</t>
+        </is>
+      </c>
+      <c r="C19" s="12">
+        <f>SUMPRODUCT((WBS!$E$6:$E$16="In presenza")*WBS!$Q$6:$Q$16)</f>
+        <v/>
+      </c>
+      <c r="D19" s="35" t="inlineStr">
+        <is>
+          <t>n.</t>
+        </is>
+      </c>
+      <c r="E19" s="36" t="inlineStr">
+        <is>
+          <t>Dalla WBS. L'Offerta § 10.1 include le trasferte per 6 incontri in presenza.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Giornate — fasi interne</t>
-        </is>
-      </c>
-      <c r="C20" s="14">
-        <f>SUMIF(WBS!$D$6:$D$17,"Interna",WBS!$W$6:$W$17)</f>
-        <v/>
-      </c>
-      <c r="D20" s="41" t="inlineStr">
-        <is>
-          <t>gg-uomo</t>
-        </is>
-      </c>
-      <c r="E20" s="42" t="inlineStr"/>
+          <t>Persone-sessione in trasferta</t>
+        </is>
+      </c>
+      <c r="C20" s="12">
+        <f>SUMPRODUCT((WBS!$E$6:$E$16="In presenza")*WBS!$Q$6:$Q$16*WBS!$S$6:$S$16)</f>
+        <v/>
+      </c>
+      <c r="D20" s="35" t="inlineStr">
+        <is>
+          <t>n.</t>
+        </is>
+      </c>
+      <c r="E20" s="36" t="inlineStr">
+        <is>
+          <t>Somma delle presenze fisiche: determina il vitto.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Costo — fasi con il cliente</t>
-        </is>
-      </c>
-      <c r="C21" s="15">
-        <f>SUMIF(WBS!$D$6:$D$17,"Cliente",WBS!$Y$6:$Y$17)</f>
-        <v/>
-      </c>
-      <c r="D21" s="41" t="inlineStr">
-        <is>
-          <t>€</t>
-        </is>
-      </c>
-      <c r="E21" s="42" t="inlineStr"/>
+          <t>Viaggi in auto</t>
+        </is>
+      </c>
+      <c r="C21" s="12">
+        <f>IF(Parametri!$C$21=0,0,ROUNDUP(C20/Parametri!$C$21,0))</f>
+        <v/>
+      </c>
+      <c r="D21" s="35" t="inlineStr">
+        <is>
+          <t>n.</t>
+        </is>
+      </c>
+      <c r="E21" s="36" t="inlineStr">
+        <is>
+          <t>Persone-sessione ÷ persone per auto. Determina km e pedaggi.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Costo — fasi interne</t>
+          <t>Ammortamento ACI</t>
         </is>
       </c>
       <c r="C22" s="15">
-        <f>SUMIF(WBS!$D$6:$D$17,"Interna",WBS!$Y$6:$Y$17)</f>
-        <v/>
-      </c>
-      <c r="D22" s="41" t="inlineStr">
+        <f>C21*Parametri!$C$17*Parametri!$C$18</f>
+        <v/>
+      </c>
+      <c r="D22" s="35" t="inlineStr">
         <is>
           <t>€</t>
         </is>
       </c>
-      <c r="E22" s="42" t="inlineStr"/>
+      <c r="E22" s="36" t="inlineStr">
+        <is>
+          <t>Viaggi × km a/r (Parametri!$C$17) × tariffa €/km (Parametri!$C$18).</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Incontri previsti con il cliente</t>
-        </is>
-      </c>
-      <c r="C23" s="12">
-        <f>SUMIF(WBS!$D$6:$D$17,"Cliente",WBS!$Q$6:$Q$17)</f>
-        <v/>
-      </c>
-      <c r="D23" s="41" t="inlineStr">
-        <is>
-          <t>n.</t>
-        </is>
-      </c>
-      <c r="E23" s="42" t="inlineStr"/>
+          <t>Pedaggi — casello</t>
+        </is>
+      </c>
+      <c r="C23" s="15">
+        <f>C21*Parametri!$C$19</f>
+        <v/>
+      </c>
+      <c r="D23" s="35" t="inlineStr">
+        <is>
+          <t>€</t>
+        </is>
+      </c>
+      <c r="E23" s="36" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Fasi con il cliente / fasi interne</t>
-        </is>
-      </c>
-      <c r="C24" s="45">
-        <f>COUNTIF(WBS!$D$6:$D$17,"Cliente")&amp;" / "&amp;COUNTIF(WBS!$D$6:$D$17,"Interna")</f>
-        <v/>
-      </c>
-      <c r="D24" s="41" t="inlineStr"/>
-      <c r="E24" s="42" t="inlineStr"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="40" t="inlineStr">
-        <is>
-          <t>›  LEAD TIME E EFFETTO DELLA PARALLELIZZAZIONE</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>Somma delle durate delle fasi, se svolte in sequenza</t>
-        </is>
-      </c>
-      <c r="C27" s="12">
-        <f>SUM(WBS!H6:H17)</f>
-        <v/>
-      </c>
-      <c r="D27" s="41" t="inlineStr">
-        <is>
-          <t>settimane</t>
-        </is>
-      </c>
-      <c r="E27" s="42" t="inlineStr">
-        <is>
-          <t>Somma aritmetica della colonna «Durata (sett.)» della WBS.</t>
-        </is>
-      </c>
+          <t>Vitto</t>
+        </is>
+      </c>
+      <c r="C24" s="15">
+        <f>C20*Parametri!$C$20</f>
+        <v/>
+      </c>
+      <c r="D24" s="35" t="inlineStr">
+        <is>
+          <t>€</t>
+        </is>
+      </c>
+      <c r="E24" s="36" t="inlineStr">
+        <is>
+          <t>Persone-sessione × costo per persona.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>TOTALE COSTO TRASFERTE</t>
+        </is>
+      </c>
+      <c r="C25" s="38">
+        <f>SUM(C22:C24)</f>
+        <v/>
+      </c>
+      <c r="D25" s="35" t="inlineStr">
+        <is>
+          <t>€</t>
+        </is>
+      </c>
+      <c r="E25" s="36" t="inlineStr"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="34" t="inlineStr">
+        <is>
+          <t>›  COSTO PIENO E MARGINE</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Lead time di calendario effettivo</t>
-        </is>
-      </c>
-      <c r="C28" s="46">
-        <f>MAX(WBS!I6:I17)-MIN(WBS!G6:G17)+1</f>
-        <v/>
-      </c>
-      <c r="D28" s="41" t="inlineStr">
-        <is>
-          <t>settimane</t>
-        </is>
-      </c>
-      <c r="E28" s="42" t="inlineStr">
-        <is>
-          <t>Prima settimana di inizio → ultima settimana di fine, tenendo conto delle fasi sovrapposte.</t>
-        </is>
-      </c>
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Costo delle giornate</t>
+        </is>
+      </c>
+      <c r="C28" s="15">
+        <f>C15</f>
+        <v/>
+      </c>
+      <c r="D28" s="35" t="inlineStr">
+        <is>
+          <t>€</t>
+        </is>
+      </c>
+      <c r="E28" s="36" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
+          <t>Costo delle trasferte</t>
+        </is>
+      </c>
+      <c r="C29" s="15">
+        <f>C25</f>
+        <v/>
+      </c>
+      <c r="D29" s="35" t="inlineStr">
+        <is>
+          <t>€</t>
+        </is>
+      </c>
+      <c r="E29" s="36" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>COSTO PIENO DI PROGETTO</t>
+        </is>
+      </c>
+      <c r="C30" s="38">
+        <f>C28+C29</f>
+        <v/>
+      </c>
+      <c r="D30" s="35" t="inlineStr">
+        <is>
+          <t>€</t>
+        </is>
+      </c>
+      <c r="E30" s="36" t="inlineStr">
+        <is>
+          <t>Giornate + trasferte. È il costo da confrontare con l'investimento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Investimento contrattuale (una tantum)</t>
+        </is>
+      </c>
+      <c r="C31" s="15">
+        <f>Parametri!$C$14</f>
+        <v/>
+      </c>
+      <c r="D31" s="35" t="inlineStr">
+        <is>
+          <t>€</t>
+        </is>
+      </c>
+      <c r="E31" s="36" t="inlineStr">
+        <is>
+          <t>Offerta § 10. Le trasferte dei 6 incontri in presenza sono già dentro questa cifra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>MARGINE DI PROGETTO</t>
+        </is>
+      </c>
+      <c r="C32" s="38">
+        <f>C31-C30</f>
+        <v/>
+      </c>
+      <c r="D32" s="35" t="inlineStr">
+        <is>
+          <t>€</t>
+        </is>
+      </c>
+      <c r="E32" s="36" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Margine percentuale</t>
+        </is>
+      </c>
+      <c r="C33" s="39">
+        <f>IF(C31=0,"",C32/C31)</f>
+        <v/>
+      </c>
+      <c r="D33" s="35" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E33" s="36" t="inlineStr">
+        <is>
+          <t>Se negativo la cella si inverte in nero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Tariffa media implicita sulle ore erogate</t>
+        </is>
+      </c>
+      <c r="C34" s="38">
+        <f>IF(C9=0,"",C31/C9)</f>
+        <v/>
+      </c>
+      <c r="D34" s="35" t="inlineStr">
+        <is>
+          <t>€/h</t>
+        </is>
+      </c>
+      <c r="E34" s="36" t="inlineStr">
+        <is>
+          <t>Investimento ÷ totale ore. Da confrontare con le tre tariffe orarie impostate nei Parametri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t>›  RIPARTIZIONE PER TIPO DI FASE</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Giornate — fasi con il cliente</t>
+        </is>
+      </c>
+      <c r="C37" s="14">
+        <f>SUMIF(WBS!$D$6:$D$16,"Cliente",WBS!$X$6:$X$16)</f>
+        <v/>
+      </c>
+      <c r="D37" s="35" t="inlineStr">
+        <is>
+          <t>gg-uomo</t>
+        </is>
+      </c>
+      <c r="E37" s="36" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Giornate — fasi interne</t>
+        </is>
+      </c>
+      <c r="C38" s="14">
+        <f>SUMIF(WBS!$D$6:$D$16,"Interna",WBS!$X$6:$X$16)</f>
+        <v/>
+      </c>
+      <c r="D38" s="35" t="inlineStr">
+        <is>
+          <t>gg-uomo</t>
+        </is>
+      </c>
+      <c r="E38" s="36" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Costo — fasi con il cliente</t>
+        </is>
+      </c>
+      <c r="C39" s="15">
+        <f>SUMIF(WBS!$D$6:$D$16,"Cliente",WBS!$Z$6:$Z$16)</f>
+        <v/>
+      </c>
+      <c r="D39" s="35" t="inlineStr">
+        <is>
+          <t>€</t>
+        </is>
+      </c>
+      <c r="E39" s="36" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>Costo — fasi interne</t>
+        </is>
+      </c>
+      <c r="C40" s="15">
+        <f>SUMIF(WBS!$D$6:$D$16,"Interna",WBS!$Z$6:$Z$16)</f>
+        <v/>
+      </c>
+      <c r="D40" s="35" t="inlineStr">
+        <is>
+          <t>€</t>
+        </is>
+      </c>
+      <c r="E40" s="36" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>Fasi con il cliente / fasi interne</t>
+        </is>
+      </c>
+      <c r="C41" s="40">
+        <f>COUNTIF(WBS!$D$6:$D$16,"Cliente")&amp;" / "&amp;COUNTIF(WBS!$D$6:$D$16,"Interna")</f>
+        <v/>
+      </c>
+      <c r="D41" s="35" t="inlineStr"/>
+      <c r="E41" s="36" t="inlineStr"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="34" t="inlineStr">
+        <is>
+          <t>›  LEAD TIME</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Somma delle durate delle fasi, se svolte in sequenza</t>
+        </is>
+      </c>
+      <c r="C44" s="12">
+        <f>SUM(WBS!H6:H16)</f>
+        <v/>
+      </c>
+      <c r="D44" s="35" t="inlineStr">
+        <is>
+          <t>settimane</t>
+        </is>
+      </c>
+      <c r="E44" s="36" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>Lead time di calendario effettivo</t>
+        </is>
+      </c>
+      <c r="C45" s="41">
+        <f>MAX(WBS!I6:I16)-MIN(WBS!G6:G16)+1</f>
+        <v/>
+      </c>
+      <c r="D45" s="35" t="inlineStr">
+        <is>
+          <t>settimane</t>
+        </is>
+      </c>
+      <c r="E45" s="36" t="inlineStr">
+        <is>
+          <t>Prima settimana di inizio → ultima settimana di fine, fasi sovrapposte incluse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
           <t>Settimane recuperate dalla parallelizzazione</t>
         </is>
       </c>
-      <c r="C29" s="12">
-        <f>C27-C28</f>
-        <v/>
-      </c>
-      <c r="D29" s="41" t="inlineStr">
+      <c r="C46" s="12">
+        <f>C44-C45</f>
+        <v/>
+      </c>
+      <c r="D46" s="35" t="inlineStr">
         <is>
           <t>settimane</t>
         </is>
       </c>
-      <c r="E29" s="42" t="inlineStr">
-        <is>
-          <t>Effetto dei workshop svolti nelle stesse due settimane.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="E46" s="36" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>Lead time target dichiarato</t>
         </is>
       </c>
-      <c r="C30" s="12">
-        <f>Parametri!$C$10</f>
-        <v/>
-      </c>
-      <c r="D30" s="41" t="inlineStr">
+      <c r="C47" s="12">
+        <f>Parametri!$C$13</f>
+        <v/>
+      </c>
+      <c r="D47" s="35" t="inlineStr">
         <is>
           <t>settimane</t>
         </is>
       </c>
-      <c r="E30" s="42" t="inlineStr">
-        <is>
-          <t>Impostato nel foglio «Parametri».</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="E47" s="36" t="inlineStr">
+        <is>
+          <t>Offerta § 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>SCOSTAMENTO effettivo vs target</t>
         </is>
       </c>
-      <c r="C31" s="46">
-        <f>C28-C30</f>
-        <v/>
-      </c>
-      <c r="D31" s="41" t="inlineStr">
+      <c r="C48" s="41">
+        <f>C45-C47</f>
+        <v/>
+      </c>
+      <c r="D48" s="35" t="inlineStr">
         <is>
           <t>settimane</t>
         </is>
       </c>
-      <c r="E31" s="42" t="inlineStr">
-        <is>
-          <t>Zero = il piano quadra. Se lo scostamento non è zero la cella si inverte in nero.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="47" t="inlineStr">
+      <c r="E48" s="36" t="inlineStr">
+        <is>
+          <t>Se diverso da zero la cella si inverte in nero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="42" t="inlineStr">
         <is>
           <t>Esito del controllo</t>
         </is>
       </c>
-      <c r="C32" s="48">
-        <f>IF(C28=C30,"Il piano quadra con il lead time target.","NON QUADRA — rivedere le settimane di inizio e le durate nella WBS.")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="40" t="inlineStr">
-        <is>
-          <t>›  IPOTESI E PUNTI APERTI</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-    </row>
-    <row r="35" ht="44" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>Pianificazione delle settimane</t>
-        </is>
-      </c>
-      <c r="C35" s="49" t="inlineStr">
-        <is>
-          <t>Il piano proposto è: S1 kick off · S2 analisi dati · S3–S4 i cinque workshop con il cliente in parallelo (revenue model, ICP e customer journey, process design, tech stack, data model) · S5 interviste qualitative a valle del process design · S6 sintesi e business case · S7 review con il cliente · S8–S9 consolidamento report · S10 presentazione. Totale 10 settimane, coerente con il target dichiarato.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="44" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>Giornate front / back / viaggio</t>
-        </is>
-      </c>
-      <c r="C36" s="49" t="inlineStr">
-        <is>
-          <t>Non ancora fornite: le celle sono vuote, sotto intestazione gialla. Finché non sono compilate, ore e costi restano a zero.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="44" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>Tariffe orarie</t>
-        </is>
-      </c>
-      <c r="C37" s="49" t="inlineStr">
-        <is>
-          <t>Non ancora fornite: da inserire nel foglio «Parametri». Sono tre tariffe distinte (front, back, viaggio).</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="44" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>Durata dei workshop</t>
-        </is>
-      </c>
-      <c r="C38" s="49" t="inlineStr">
-        <is>
-          <t>Da definire per revenue model, ICP e customer journey, process design, tech stack, data model e presentazione finale (colonna «Durata incontro (h)» della WBS).</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="44" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>Modalità da confermare</t>
-        </is>
-      </c>
-      <c r="C39" s="49" t="inlineStr">
-        <is>
-          <t>Tech stack, data model e presentazione finale sono impostati su «Da definire»: da scegliere fra presenza e remoto. La scelta incide sulle giornate di viaggio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="44" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>Somma sequenziale vs lead time</t>
-        </is>
-      </c>
-      <c r="C40" s="49" t="inlineStr">
-        <is>
-          <t>La somma delle durate di fase vale 18 settimane perché le cinque fasi in parallelo occupano ciascuna la stessa finestra di 2 settimane. Il lead time reale resta 10 settimane: è questo il numero da leggere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="44" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="C49" s="43">
+        <f>IF(C45=C47,"Il piano quadra con il lead time target.","Scostamento sul target: la coda di redazione in lingua inglese cade oltre le 10 settimane.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="34" t="inlineStr">
+        <is>
+          <t>›  IPOTESI, SCOSTAMENTI E PUNTI APERTI</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+    </row>
+    <row r="52" ht="46" customHeight="1">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>Fonte del piano</t>
+        </is>
+      </c>
+      <c r="C52" s="44" t="inlineStr">
+        <is>
+          <t>Offerta CX260803_Off_Laica_RevOps assessment B2B e B2C v1.1 del 28 ago 2026. Modalità, ore e numero di sessioni di ciascuna fase sono letti dal capitolo 6 del contratto. Le 6 sessioni in presenza coincidono con le 6 trasferte incluse nell'investimento al § 10.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="46" customHeight="1">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>Risorse per sessione: 3 anziché 2</t>
+        </is>
+      </c>
+      <c r="C53" s="44" t="inlineStr">
+        <is>
+          <t>Il contratto indica 2 risorse Impresoft su kick-off e Workshop #1-#4, e 4 sul § 6.6 (Workshop #5 e presentazione). La WBS pianifica 3 persone su tutte le sessioni con il cliente — 1 facilitatore senior + 2 RevOps Consultant junior — come da indicazione. Sul Workshop #2, che vale 2 sessioni da 6 ore, la terza persona costa 1,5 giornate front in più.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="46" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>Ruoli generici invece di ruoli specialistici</t>
+        </is>
+      </c>
+      <c r="C54" s="44" t="inlineStr">
+        <is>
+          <t>Il contratto nomina CX Strategist, Process Analyst e Integration Expert su workshop specifici. Nella WBS le persone sono indicate come «RevOps Consultant junior» senza specializzazione funzionale, per scelta di pianificazione. Sulle sessioni corrispondenti il contratto promette al cliente una competenza dedicata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="46" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>Giornate back office: stime, non contratto</t>
+        </is>
+      </c>
+      <c r="C55" s="44" t="inlineStr">
+        <is>
+          <t>Il contratto quantifica solo le ore erogate al cliente e il numero di trasferte. Le giornate back office della WBS sono stime Impresoft e sono la variabile su cui si gioca il margine: la voce più pesante è il consolidamento del report, roadmap e business case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="46" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>Interviste one-to-one</t>
+        </is>
+      </c>
+      <c r="C56" s="44" t="inlineStr">
+        <is>
+          <t>Il contratto (§ 6.4) le colloca DENTRO il Workshop #3 e ne fissa il numero — 5 — ma non la durata. Nella WBS sono un blocco a sé per separare i momenti di progetto; 1 ora ciascuna è una stima.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="46" customHeight="1">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>Review con il cliente: fuori perimetro</t>
+        </is>
+      </c>
+      <c r="C57" s="44" t="inlineStr">
+        <is>
+          <t>L'Offerta non prevede una sessione di validazione tra il Workshop #5 e il meeting di presentazione. La fase 8 è mantenuta su richiesta: la sua durata è da definire e finché è vuota non genera giornate front.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="46" customHeight="1">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>Roadmap</t>
+        </is>
+      </c>
+      <c r="C58" s="44" t="inlineStr">
+        <is>
+          <t>Non è una fase. È contenuto del Workshop #5 (prioritizzazione) e deliverable del report finale, come previsto dal § 6.6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="46" customHeight="1">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>Vincolo dei 15 giorni</t>
+        </is>
+      </c>
+      <c r="C59" s="44" t="inlineStr">
+        <is>
+          <t>Il § 6.6 fissa il meeting di presentazione a circa 15 giorni dopo il Workshop #5. Nel piano proposto: Workshop #5 in S8, presentazione in S10. Spostando una delle due settimane, il vincolo va riverificato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="46" customHeight="1">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>Output in lingua inglese</t>
+        </is>
+      </c>
+      <c r="C60" s="44" t="inlineStr">
+        <is>
+          <t>Deliverable obbligatorio del § 6.6, da redigere DOPO il meeting di presentazione. Ma il § 6.7 esclude dall'offerta la «traduzione di testi» come servizio di terze parti: la versione inglese è a carico interno. È la fase 11 e cade oltre le 10 settimane dichiarate al § 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="46" customHeight="1">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>Durate contrattuali dichiarate due volte</t>
+        </is>
+      </c>
+      <c r="C61" s="44" t="inlineStr">
+        <is>
+          <t>Il § 6 dichiara «8-10 settimane», il § 8 dichiara «10 settimane». Incoerenza interna al contratto, da sanare prima della firma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="46" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>Fatturazione</t>
+        </is>
+      </c>
+      <c r="C62" s="44" t="inlineStr">
+        <is>
+          <t>50% alla sottoscrizione, 50% nel mese in cui il PDF con l'output viene anticipato via e-mail al cliente (§ 11). Il trigger della seconda fattura è la fase 9, non la presentazione.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="46" customHeight="1">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>Identità visiva</t>
         </is>
       </c>
-      <c r="C41" s="49" t="inlineStr">
-        <is>
-          <t>Palette Impresoft di tre colori (giallo #FDC300, nero, bianco) più grigi puri derivati dal nero. Font Manrope, fallback Arial. Nessun colore semantico: verde e rosso sono stati sostituiti dalla scala monocroma e da etichette in parole.</t>
+      <c r="C63" s="44" t="inlineStr">
+        <is>
+          <t>Palette Impresoft di tre colori (giallo #FDC300, nero, bianco) più grigi puri derivati dal nero. Font Manrope, fallback Arial. Nessun colore semantico: gli stati usano la scala monocroma e le parole.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A12:E12"/>
+  <mergeCells count="22">
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="C58:E58"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="C63:E63"/>
   </mergeCells>
-  <conditionalFormatting sqref="C31">
+  <conditionalFormatting sqref="C32">
     <cfRule type="expression" priority="1" dxfId="5" stopIfTrue="1">
-      <formula>C31&lt;&gt;0</formula>
+      <formula>C32&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C32:E32">
+  <conditionalFormatting sqref="C33">
     <cfRule type="expression" priority="2" dxfId="5" stopIfTrue="1">
-      <formula>$C$28&lt;&gt;$C$30</formula>
+      <formula>C33&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C48">
+    <cfRule type="expression" priority="3" dxfId="5" stopIfTrue="1">
+      <formula>C48&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C49:E49">
+    <cfRule type="expression" priority="4" dxfId="5" stopIfTrue="1">
+      <formula>$C$45&lt;&gt;$C$47</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4252,14 +4466,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="2" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="56" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -4274,9 +4488,9 @@
       <c r="E1" s="2" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="39" t="inlineStr">
-        <is>
-          <t>Le celle con riquadro nero, sotto l'intestazione gialla, sono da compilare. Tutto il resto del file si ricalcola da qui: modificando un valore in questa pagina si aggiornano ore e costi di tutte le fasi.</t>
+      <c r="A2" s="33" t="inlineStr">
+        <is>
+          <t>Le celle con riquadro nero, sotto l'intestazione gialla, sono da compilare. Tutto il file si ricalcola da qui: giornate front office e viaggio, ore, costi e costo delle trasferte.</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4500,7 @@
           <t>Parametro</t>
         </is>
       </c>
-      <c r="B4" s="50" t="n"/>
+      <c r="B4" s="45" t="n"/>
       <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Valore</t>
@@ -4303,124 +4517,290 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>›  IMPEGNO E TARIFFE</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Ore per giornata</t>
         </is>
       </c>
-      <c r="B5" s="51" t="n"/>
-      <c r="C5" s="11" t="n">
+      <c r="B6" s="46" t="n"/>
+      <c r="C6" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="D5" s="41" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>Base di conversione giornate → ore. Confermato: 8 ore.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Base di conversione giornate → ore.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Tariffa oraria — Front office</t>
         </is>
       </c>
-      <c r="B6" s="51" t="n"/>
-      <c r="C6" s="52" t="n"/>
-      <c r="D6" s="41" t="inlineStr">
+      <c r="B7" s="46" t="n"/>
+      <c r="C7" s="47" t="n"/>
+      <c r="D7" s="35" t="inlineStr">
         <is>
           <t>€/h</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>Ore erogate presso il cliente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Ore erogate al cliente, incontri in remoto inclusi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Tariffa oraria — Back office</t>
         </is>
       </c>
-      <c r="B7" s="51" t="n"/>
-      <c r="C7" s="52" t="n"/>
-      <c r="D7" s="41" t="inlineStr">
+      <c r="B8" s="46" t="n"/>
+      <c r="C8" s="47" t="n"/>
+      <c r="D8" s="35" t="inlineStr">
         <is>
           <t>€/h</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>Ore di lavoro interno (analisi, delivery, reportistica).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Lavoro interno: analisi, delivery, reportistica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Tariffa oraria — Viaggio</t>
         </is>
       </c>
-      <c r="B8" s="51" t="n"/>
-      <c r="C8" s="52" t="n"/>
-      <c r="D8" s="41" t="inlineStr">
+      <c r="B9" s="46" t="n"/>
+      <c r="C9" s="47" t="n"/>
+      <c r="D9" s="35" t="inlineStr">
         <is>
           <t>€/h</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>Ore di trasferimento. Incluse nel monte ore complessivo di progetto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Tempo di trasferimento. Incluso nel monte ore di progetto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
+          <t>Ore di viaggio per trasferta (a/r, per persona)</t>
+        </is>
+      </c>
+      <c r="B10" s="46" t="n"/>
+      <c r="C10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="35" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Vicenza ↔ Barbarano Mossano, ~25 km per tratta. STIMA, non contrattuale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t>›  PROGETTO</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
           <t>Lead time target di progetto</t>
         </is>
       </c>
-      <c r="B10" s="51" t="n"/>
-      <c r="C10" s="11" t="n">
+      <c r="B13" s="46" t="n"/>
+      <c r="C13" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="D10" s="41" t="inlineStr">
+      <c r="D13" s="35" t="inlineStr">
         <is>
           <t>settimane</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>Durata di calendario dichiarata in fase di impostazione.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="37" t="inlineStr">
-        <is>
-          <t>Riferimenti usati dalle formule</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="39" t="inlineStr">
-        <is>
-          <t>Ore per giornata = Parametri!$C$5   ·   Tariffe = $C$6 / $C$7 / $C$8   ·   Lead time target = $C$10</t>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>Offerta § 8. Il § 6 dichiara invece 8-10 settimane: incoerenza interna al contratto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Investimento contrattuale (una tantum)</t>
+        </is>
+      </c>
+      <c r="B14" s="46" t="n"/>
+      <c r="C14" s="47" t="n">
+        <v>27000</v>
+      </c>
+      <c r="D14" s="35" t="inlineStr">
+        <is>
+          <t>€</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Offerta § 10. Comprende già i costi di trasferta dei 6 incontri in presenza (§ 10.1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>›  COSTO DELLE TRASFERTE (già incluso nell'investimento)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Km andata e ritorno per trasferta</t>
+        </is>
+      </c>
+      <c r="B17" s="46" t="n"/>
+      <c r="C17" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D17" s="35" t="inlineStr">
+        <is>
+          <t>km</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>STIMA sulle sedi indicate al § 10.1 (Barbarano Mossano ↔ Vicenza).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Ammortamento ACI</t>
+        </is>
+      </c>
+      <c r="B18" s="46" t="n"/>
+      <c r="C18" s="47" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D18" s="35" t="inlineStr">
+        <is>
+          <t>€/km</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Tariffa indicata al § 10.1 dell'Offerta per le trasferte fuori perimetro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Pedaggi — casello</t>
+        </is>
+      </c>
+      <c r="B19" s="46" t="n"/>
+      <c r="C19" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="35" t="inlineStr">
+        <is>
+          <t>€/auto/trasferta</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>Tratta ordinaria: default 0. Da correggere se il percorso prevede autostrada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Vitto</t>
+        </is>
+      </c>
+      <c r="B20" s="46" t="n"/>
+      <c r="C20" s="47" t="n"/>
+      <c r="D20" s="35" t="inlineStr">
+        <is>
+          <t>€/persona/trasferta</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Da compilare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Persone per auto</t>
+        </is>
+      </c>
+      <c r="B21" s="46" t="n"/>
+      <c r="C21" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" s="35" t="inlineStr">
+        <is>
+          <t>n.</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Quante persone viaggiano insieme: determina il numero di viaggi auto.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
+    <mergeCell ref="A12:E12"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
@@ -4434,14 +4814,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -4455,10 +4835,10 @@
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
     </row>
-    <row r="2">
-      <c r="A2" s="39" t="inlineStr">
-        <is>
-          <t>Compilare la colonna Nome. I ruoli sono quelli richiamati nelle colonne Owner e Partecipanti della WBS.</t>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="33" t="inlineStr">
+        <is>
+          <t>Compilare la colonna Nome. Sulla WBS le persone sono indicate come «facilitatore senior» e «RevOps Consultant junior» senza specializzazione funzionale, per scelta di pianificazione.</t>
         </is>
       </c>
     </row>
@@ -4489,129 +4869,144 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Commerciale</t>
         </is>
       </c>
-      <c r="B5" s="53" t="n"/>
-      <c r="C5" s="41" t="inlineStr">
+      <c r="B5" s="48" t="n"/>
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>Senior</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Fase 1 — convocazione kick off</t>
+          <t>Fase 1 — convocazione del kick-off</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>Invia la prima email al cliente per fissare il kick off.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>Nell'Offerta il responsabile è il Sales Manager.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="B6" s="53" t="n"/>
-      <c r="C6" s="41" t="inlineStr">
+      <c r="B6" s="48" t="n"/>
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>Senior</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Fasi 1 → 12 — presidio di progetto</t>
+          <t>Fasi 1 → 11 — presidio di progetto</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Invia il follow-up post kick off con documento presentato e tracciato dati. Owner del piano.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>Referente unico verso il Cliente (Offerta § 7). Owner del piano di lavoro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Facilitatore senior</t>
         </is>
       </c>
-      <c r="B7" s="53" t="inlineStr">
+      <c r="B7" s="48" t="inlineStr">
         <is>
           <t>Alessandro Bruti</t>
         </is>
       </c>
-      <c r="C7" s="41" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>Senior</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Tutti i workshop con il cliente</t>
+          <t>Tutte le sessioni con il cliente</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Conduce i workshop di revenue model, ICP, process design, tech stack e data model.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+          <t>Conduce i workshop. Nell'Offerta corrisponde al RevOps Consultant senior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Consulente RevOps junior 1</t>
-        </is>
-      </c>
-      <c r="B8" s="53" t="n"/>
-      <c r="C8" s="41" t="inlineStr">
+          <t>RevOps Consultant junior 1</t>
+        </is>
+      </c>
+      <c r="B8" s="48" t="n"/>
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>Junior</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Workshop + back office</t>
+          <t>Sessioni con il cliente + back office</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>In presenza ai workshop; analisi dati e compilazione file di delivery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
+          <t>Nell'Offerta le figure specialistiche sono CX Strategist, Process Analyst e Integration Expert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Consulente RevOps junior 2</t>
-        </is>
-      </c>
-      <c r="B9" s="53" t="n"/>
-      <c r="C9" s="41" t="inlineStr">
+          <t>RevOps Consultant junior 2</t>
+        </is>
+      </c>
+      <c r="B9" s="48" t="n"/>
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>Junior</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Workshop + back office</t>
+          <t>Sessioni con il cliente + back office</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>In presenza ai workshop; supporto alla delivery.</t>
+          <t>Conduce le 5 interviste one-to-one della fase 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>Lato Laica S.p.A. (Offerta § 6 e § 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="44" t="inlineStr">
+        <is>
+          <t>Riccardo Dolcetta — Managing Director · Nicolò Zanuso — CFO · più, a seconda della sessione: CMO / Marketing Manager, CSO, referente servizio clienti, referenti IT e gestione dati, key user operativi.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
